--- a/Transrail_DCF.xlsx
+++ b/Transrail_DCF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jimit\Desktop\Avalon Research\Company\Transrail Lighting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D677420-E6C5-498C-A374-9BFF005A4F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7497BA8-4598-465B-9EBA-BEE522B54CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DCF &amp; Valuation" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="171">
   <si>
     <t>Input Parameter</t>
   </si>
@@ -607,6 +607,9 @@
   </si>
   <si>
     <t>CMP  (₹) - live from CMP Input</t>
+  </si>
+  <si>
+    <t>Equity Capital</t>
   </si>
 </sst>
 </file>
@@ -621,9 +624,9 @@
     <numFmt numFmtId="167" formatCode="#,##0.0000000000000"/>
     <numFmt numFmtId="168" formatCode="0.00%;\-0.00%;&quot;- &quot;"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="173" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -728,6 +731,13 @@
     <font>
       <sz val="10"/>
       <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF002060"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -976,38 +986,38 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1015,7 +1025,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -1027,13 +1037,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1381,7 +1384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q115"/>
+  <dimension ref="A1:Q116"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.88671875" style="12" bestFit="1" customWidth="1"/>
@@ -1397,11 +1400,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="68" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
@@ -1443,1643 +1446,1653 @@
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="68">
-        <v>13.3775</v>
-      </c>
-      <c r="C6" s="70" t="s">
-        <v>114</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="B6" s="38">
+        <v>26.85</v>
+      </c>
+      <c r="C6" s="39"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="38">
-        <v>524</v>
-      </c>
-      <c r="C7" s="70" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="B7" s="65">
+        <f>B6/B5</f>
+        <v>13.425000000000001</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="13">
-        <f>B7*B6</f>
-        <v>7009.8099999999995</v>
-      </c>
-      <c r="C8" s="70"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="38">
+        <v>513</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="38">
-        <v>842.79</v>
-      </c>
-      <c r="C9" s="70" t="s">
-        <v>115</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B9" s="13">
+        <f>B8*B7</f>
+        <v>6887.0250000000005</v>
+      </c>
+      <c r="C9" s="63"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="38">
-        <v>481.14</v>
-      </c>
-      <c r="C10" s="70" t="s">
-        <v>9</v>
+        <v>842.79</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="13">
-        <f>B9-B10</f>
-        <v>361.65</v>
-      </c>
-      <c r="C11" s="70" t="s">
-        <v>116</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="38">
+        <v>481.14</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13">
+        <f>B10-B11</f>
+        <v>361.65</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="13">
-        <f>B8+B11</f>
-        <v>7371.4599999999991</v>
-      </c>
-      <c r="C12" s="70" t="s">
+      <c r="B13" s="13">
+        <f>B9+B12</f>
+        <v>7248.6750000000002</v>
+      </c>
+      <c r="C13" s="63" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="40"/>
-    </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="66" t="s">
+      <c r="B15" s="40"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="65" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="66" t="s">
         <v>153</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="B18" s="41">
-        <v>6900.4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="42">
-        <v>0.2</v>
-      </c>
-      <c r="D19" s="42">
-        <v>0.2</v>
-      </c>
-      <c r="E19" s="42">
-        <v>0.2</v>
+      <c r="B19" s="41">
+        <v>7325.0399999999991</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="42">
+        <v>0.24</v>
+      </c>
+      <c r="D20" s="42">
+        <v>0.22</v>
+      </c>
+      <c r="E20" s="42">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="42">
+      <c r="C21" s="42">
+        <v>0.27</v>
+      </c>
+      <c r="D21" s="42">
         <v>0.25</v>
       </c>
-      <c r="D20" s="42">
+      <c r="E21" s="42">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="42">
+        <v>0.3</v>
+      </c>
+      <c r="D22" s="42">
+        <v>0.27</v>
+      </c>
+      <c r="E22" s="42">
         <v>0.25</v>
       </c>
-      <c r="E20" s="42">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" s="42">
-        <v>0.3</v>
-      </c>
-      <c r="D21" s="42">
-        <v>0.3</v>
-      </c>
-      <c r="E21" s="42">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="65" t="s">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="66" t="s">
         <v>154</v>
       </c>
-      <c r="B22" s="65"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="42">
-        <v>0.11</v>
-      </c>
-      <c r="D23" s="42">
-        <v>0.11</v>
-      </c>
-      <c r="E23" s="42">
-        <v>0.11</v>
-      </c>
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="42">
-        <v>0.13200000000000001</v>
+        <v>0.105</v>
       </c>
       <c r="D24" s="42">
-        <v>0.13200000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E24" s="42">
-        <v>0.13200000000000001</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="42">
+        <v>0.12482851401053319</v>
+      </c>
+      <c r="D25" s="42">
+        <v>0.11985724729266471</v>
+      </c>
+      <c r="E25" s="42">
+        <v>0.12010017373026666</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="42">
+      <c r="C26" s="42">
         <v>0.14499999999999999</v>
       </c>
-      <c r="D25" s="42">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="E25" s="42">
-        <v>0.14499999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="65" t="s">
+      <c r="D26" s="42">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E26" s="42">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="B26" s="65"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
+      <c r="B27" s="66"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="44">
+      <c r="B28" s="44">
         <f>Assumptions!B17</f>
         <v>0.25169999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B28" s="41">
-        <v>130.30000000000001</v>
-      </c>
-    </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B29" s="41">
-        <v>143.19999999999999</v>
+        <v>130.30000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B30" s="41">
-        <v>136.30000000000001</v>
+        <v>143.19999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B31" s="41">
-        <v>195</v>
+        <v>149.5</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B32" s="41">
-        <v>108.7</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B33" s="41">
-        <v>135.9</v>
+        <v>174.4</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B34" s="41">
-        <v>70.599999999999994</v>
+        <v>216.3</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B35" s="41">
-        <v>126.4</v>
+        <v>346.9</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" s="41">
+        <v>475.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B36" s="41">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="65" t="s">
+      <c r="B37" s="41">
+        <v>512.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="66" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="65"/>
-      <c r="C37" s="65"/>
-    </row>
-    <row r="38" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+    </row>
+    <row r="39" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="B38" s="44">
+      <c r="B39" s="44">
         <f>Assumptions!B4</f>
         <v>6.0309999999999996E-2</v>
       </c>
-      <c r="C38" s="71" t="s">
+      <c r="C39" s="69" t="s">
         <v>160</v>
       </c>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B39" s="44">
-        <f>Assumptions!B13</f>
-        <v>9.2862435457037068E-2</v>
-      </c>
-      <c r="C39" s="71"/>
       <c r="D39" s="19"/>
       <c r="E39" s="19"/>
       <c r="F39" s="19"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" s="27">
-        <f>Assumptions!B18</f>
-        <v>1.3044376921972554</v>
-      </c>
-      <c r="C40" s="71"/>
+        <v>135</v>
+      </c>
+      <c r="B40" s="44">
+        <f>Assumptions!B13</f>
+        <v>9.2862435457037068E-2</v>
+      </c>
+      <c r="C40" s="69"/>
       <c r="D40" s="19"/>
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B41" s="45">
-        <f>Assumptions!B22</f>
-        <v>0.10696734059097979</v>
-      </c>
-      <c r="C41" s="71"/>
+        <v>50</v>
+      </c>
+      <c r="B41" s="27">
+        <f>Assumptions!B18</f>
+        <v>1.3044376921972554</v>
+      </c>
+      <c r="C41" s="69"/>
       <c r="D41" s="19"/>
       <c r="E41" s="19"/>
       <c r="F41" s="19"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B42" s="44">
-        <f>Assumptions!B23</f>
-        <v>0.25169999999999998</v>
-      </c>
-      <c r="C42" s="71"/>
+        <v>24</v>
+      </c>
+      <c r="B42" s="45">
+        <f>Assumptions!B22</f>
+        <v>0.10696734059097979</v>
+      </c>
+      <c r="C42" s="69"/>
       <c r="D42" s="19"/>
       <c r="E42" s="19"/>
       <c r="F42" s="19"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B43" s="46">
-        <f>Assumptions!B27</f>
-        <v>2401</v>
-      </c>
-      <c r="C43" s="71"/>
+        <v>25</v>
+      </c>
+      <c r="B43" s="44">
+        <f>Assumptions!B23</f>
+        <v>0.25169999999999998</v>
+      </c>
+      <c r="C43" s="69"/>
       <c r="D43" s="19"/>
       <c r="E43" s="19"/>
       <c r="F43" s="19"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B44" s="46">
-        <f>Assumptions!B26</f>
-        <v>815</v>
-      </c>
-      <c r="C44" s="71"/>
+        <f>Assumptions!B27</f>
+        <v>2401</v>
+      </c>
+      <c r="C44" s="69"/>
       <c r="D44" s="19"/>
       <c r="E44" s="19"/>
       <c r="F44" s="19"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="25">
-        <f>Assumptions!B29</f>
-        <v>0.15574653400043303</v>
-      </c>
-      <c r="C45" s="71"/>
+        <v>8</v>
+      </c>
+      <c r="B45" s="46">
+        <f>Assumptions!B26</f>
+        <v>815</v>
+      </c>
+      <c r="C45" s="69"/>
       <c r="D45" s="19"/>
       <c r="E45" s="19"/>
       <c r="F45" s="19"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="45">
-        <f>Assumptions!B31</f>
-        <v>0.04</v>
-      </c>
-      <c r="C46" s="71"/>
+        <v>45</v>
+      </c>
+      <c r="B46" s="25">
+        <f>Assumptions!B29</f>
+        <v>0.15574653400043303</v>
+      </c>
+      <c r="C46" s="69"/>
       <c r="D46" s="19"/>
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" s="45">
+        <f>Assumptions!B31</f>
+        <v>0.04</v>
+      </c>
+      <c r="C47" s="69"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B47" s="47">
+      <c r="B48" s="47">
         <f>Assumptions!B33</f>
         <v>10</v>
       </c>
-      <c r="C47" s="71"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="66" t="s">
+      <c r="C48" s="69"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="68" t="s">
         <v>157</v>
       </c>
-      <c r="B49" s="66"/>
-      <c r="C49" s="66"/>
-      <c r="D49" s="66"/>
-      <c r="E49" s="66"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="68"/>
+      <c r="C50" s="68"/>
+      <c r="D50" s="68"/>
+      <c r="E50" s="68"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C51" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D51" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E51" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="65" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="66" t="s">
         <v>158</v>
       </c>
-      <c r="B51" s="65"/>
-      <c r="C51" s="65"/>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="13" t="s">
+      <c r="B52" s="66"/>
+      <c r="C52" s="66"/>
+      <c r="D52" s="66"/>
+      <c r="E52" s="66"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C52" s="8">
-        <f>'DCF &amp; Valuation'!C19</f>
+      <c r="C53" s="8">
+        <f>'DCF &amp; Valuation'!C20</f>
+        <v>0.24</v>
+      </c>
+      <c r="D53" s="8">
+        <f>'DCF &amp; Valuation'!D20</f>
+        <v>0.22</v>
+      </c>
+      <c r="E53" s="8">
+        <f>'DCF &amp; Valuation'!E20</f>
         <v>0.2</v>
       </c>
-      <c r="D52" s="8">
-        <f>'DCF &amp; Valuation'!D19</f>
-        <v>0.2</v>
-      </c>
-      <c r="E52" s="8">
-        <f>'DCF &amp; Valuation'!E19</f>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="14" t="s">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C53" s="9">
-        <f>'DCF &amp; Valuation'!C20</f>
+      <c r="C54" s="9">
+        <f>'DCF &amp; Valuation'!C21</f>
+        <v>0.27</v>
+      </c>
+      <c r="D54" s="9">
+        <f>'DCF &amp; Valuation'!D21</f>
         <v>0.25</v>
       </c>
-      <c r="D53" s="9">
-        <f>'DCF &amp; Valuation'!D20</f>
-        <v>0.25</v>
-      </c>
-      <c r="E53" s="9">
-        <f>'DCF &amp; Valuation'!E20</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C54" s="8">
-        <f>'DCF &amp; Valuation'!C21</f>
-        <v>0.3</v>
-      </c>
-      <c r="D54" s="8">
-        <f>'DCF &amp; Valuation'!D21</f>
-        <v>0.3</v>
-      </c>
-      <c r="E54" s="8">
+      <c r="E54" s="9">
         <f>'DCF &amp; Valuation'!E21</f>
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="8">
+        <f>'DCF &amp; Valuation'!C22</f>
+        <v>0.3</v>
+      </c>
+      <c r="D55" s="8">
+        <f>'DCF &amp; Valuation'!D22</f>
+        <v>0.27</v>
+      </c>
+      <c r="E55" s="8">
+        <f>'DCF &amp; Valuation'!E22</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B55" s="3">
-        <f>'DCF &amp; Valuation'!B18</f>
-        <v>6900.4</v>
-      </c>
-      <c r="C55" s="3">
-        <f t="shared" ref="C55:E57" si="0">B55*(1+C52)</f>
-        <v>8280.48</v>
-      </c>
-      <c r="D55" s="3">
-        <f t="shared" si="0"/>
-        <v>9936.5759999999991</v>
-      </c>
-      <c r="E55" s="3">
-        <f t="shared" si="0"/>
-        <v>11923.891199999998</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="14" t="s">
+      <c r="B56" s="3">
+        <f>'DCF &amp; Valuation'!B19</f>
+        <v>7325.0399999999991</v>
+      </c>
+      <c r="C56" s="3">
+        <f t="shared" ref="C56:E58" si="0">B56*(1+C53)</f>
+        <v>9083.0495999999985</v>
+      </c>
+      <c r="D56" s="3">
+        <f t="shared" si="0"/>
+        <v>11081.320511999998</v>
+      </c>
+      <c r="E56" s="3">
+        <f t="shared" si="0"/>
+        <v>13297.584614399997</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B56" s="10">
-        <f>'DCF &amp; Valuation'!B18</f>
-        <v>6900.4</v>
-      </c>
-      <c r="C56" s="10">
-        <f t="shared" si="0"/>
-        <v>8625.5</v>
-      </c>
-      <c r="D56" s="10">
-        <f t="shared" si="0"/>
-        <v>10781.875</v>
-      </c>
-      <c r="E56" s="10">
-        <f t="shared" si="0"/>
-        <v>13477.34375</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="13" t="s">
+      <c r="B57" s="10">
+        <f>'DCF &amp; Valuation'!B19</f>
+        <v>7325.0399999999991</v>
+      </c>
+      <c r="C57" s="10">
+        <f t="shared" si="0"/>
+        <v>9302.8007999999991</v>
+      </c>
+      <c r="D57" s="10">
+        <f t="shared" si="0"/>
+        <v>11628.500999999998</v>
+      </c>
+      <c r="E57" s="10">
+        <f t="shared" si="0"/>
+        <v>14419.341239999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B57" s="3">
-        <f>'DCF &amp; Valuation'!B18</f>
-        <v>6900.4</v>
-      </c>
-      <c r="C57" s="3">
-        <f t="shared" si="0"/>
-        <v>8970.52</v>
-      </c>
-      <c r="D57" s="3">
-        <f t="shared" si="0"/>
-        <v>11661.676000000001</v>
-      </c>
-      <c r="E57" s="3">
-        <f t="shared" si="0"/>
-        <v>15160.178800000002</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="65" t="s">
+      <c r="B58" s="3">
+        <f>'DCF &amp; Valuation'!B19</f>
+        <v>7325.0399999999991</v>
+      </c>
+      <c r="C58" s="3">
+        <f t="shared" si="0"/>
+        <v>9522.5519999999997</v>
+      </c>
+      <c r="D58" s="3">
+        <f t="shared" si="0"/>
+        <v>12093.64104</v>
+      </c>
+      <c r="E58" s="3">
+        <f t="shared" si="0"/>
+        <v>15117.051300000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="66" t="s">
         <v>159</v>
       </c>
-      <c r="B59" s="65"/>
-      <c r="C59" s="4" t="s">
+      <c r="B60" s="66"/>
+      <c r="C60" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D60" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E60" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="13" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C60" s="8">
-        <f>'DCF &amp; Valuation'!C23</f>
-        <v>0.11</v>
-      </c>
-      <c r="D60" s="8">
-        <f>'DCF &amp; Valuation'!D23</f>
-        <v>0.11</v>
-      </c>
-      <c r="E60" s="8">
-        <f>'DCF &amp; Valuation'!E23</f>
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="14" t="s">
+      <c r="C61" s="8">
+        <f>'DCF &amp; Valuation'!C24</f>
+        <v>0.105</v>
+      </c>
+      <c r="D61" s="8">
+        <f>'DCF &amp; Valuation'!D24</f>
+        <v>0.1</v>
+      </c>
+      <c r="E61" s="8">
+        <f>'DCF &amp; Valuation'!E24</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C61" s="9">
-        <f>'DCF &amp; Valuation'!C24</f>
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="D61" s="9">
-        <f>'DCF &amp; Valuation'!D24</f>
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="E61" s="9">
-        <f>'DCF &amp; Valuation'!E24</f>
-        <v>0.13200000000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C62" s="8">
+      <c r="C62" s="9">
         <f>'DCF &amp; Valuation'!C25</f>
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="D62" s="8">
+        <v>0.12482851401053319</v>
+      </c>
+      <c r="D62" s="9">
         <f>'DCF &amp; Valuation'!D25</f>
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="E62" s="8">
+        <v>0.11985724729266471</v>
+      </c>
+      <c r="E62" s="9">
         <f>'DCF &amp; Valuation'!E25</f>
-        <v>0.14499999999999999</v>
+        <v>0.12010017373026666</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="8">
+        <f>'DCF &amp; Valuation'!C26</f>
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="D63" s="8">
+        <f>'DCF &amp; Valuation'!D26</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E63" s="8">
+        <f>'DCF &amp; Valuation'!E26</f>
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C63" s="3">
-        <f t="shared" ref="C63:E65" si="1">C55*C60</f>
-        <v>910.8528</v>
-      </c>
-      <c r="D63" s="3">
+      <c r="C64" s="3">
+        <f t="shared" ref="C64:E66" si="1">C56*C61</f>
+        <v>953.72020799999984</v>
+      </c>
+      <c r="D64" s="3">
         <f t="shared" si="1"/>
-        <v>1093.0233599999999</v>
-      </c>
-      <c r="E63" s="3">
+        <v>1108.1320512</v>
+      </c>
+      <c r="E64" s="3">
         <f t="shared" si="1"/>
-        <v>1311.6280319999998</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="14" t="s">
+        <v>1329.7584614399998</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A65" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C65" s="10">
         <f t="shared" si="1"/>
-        <v>1138.566</v>
-      </c>
-      <c r="D64" s="10">
+        <v>1161.2547999999992</v>
+      </c>
+      <c r="D65" s="10">
         <f t="shared" si="1"/>
-        <v>1423.2075</v>
-      </c>
-      <c r="E64" s="10">
+        <v>1393.7601199999988</v>
+      </c>
+      <c r="E65" s="10">
         <f t="shared" si="1"/>
-        <v>1779.0093750000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A65" s="13" t="s">
+        <v>1731.7653879999984</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A66" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C66" s="3">
         <f t="shared" si="1"/>
-        <v>1300.7254</v>
-      </c>
-      <c r="D65" s="3">
+        <v>1380.7700399999999</v>
+      </c>
+      <c r="D66" s="3">
         <f t="shared" si="1"/>
-        <v>1690.9430200000002</v>
-      </c>
-      <c r="E65" s="3">
+        <v>1693.1097456000002</v>
+      </c>
+      <c r="E66" s="3">
         <f t="shared" si="1"/>
-        <v>2198.2259260000001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A67" s="65" t="s">
+        <v>2116.3871820000004</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A68" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="B67" s="65"/>
-      <c r="C67" s="4" t="s">
+      <c r="B68" s="66"/>
+      <c r="C68" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D68" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E68" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G67" s="65" t="s">
+      <c r="G68" s="66" t="s">
         <v>161</v>
       </c>
-      <c r="H67" s="65"/>
-      <c r="I67" s="4" t="s">
+      <c r="H68" s="66"/>
+      <c r="I68" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J67" s="4" t="s">
+      <c r="J68" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K67" s="4" t="s">
+      <c r="K68" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="M67" s="65" t="s">
+      <c r="M68" s="66" t="s">
         <v>163</v>
       </c>
-      <c r="N67" s="65"/>
-      <c r="O67" s="4" t="s">
+      <c r="N68" s="66"/>
+      <c r="O68" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P67" s="4" t="s">
+      <c r="P68" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q67" s="4" t="s">
+      <c r="Q68" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A68" s="15" t="s">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A69" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B68" s="16"/>
-      <c r="C68" s="5">
+      <c r="B69" s="16"/>
+      <c r="C69" s="5">
+        <f>C65</f>
+        <v>1161.2547999999992</v>
+      </c>
+      <c r="D69" s="5">
+        <f>D65</f>
+        <v>1393.7601199999988</v>
+      </c>
+      <c r="E69" s="5">
+        <f>E65</f>
+        <v>1731.7653879999984</v>
+      </c>
+      <c r="G69" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H69" s="16"/>
+      <c r="I69" s="5">
         <f>C64</f>
-        <v>1138.566</v>
-      </c>
-      <c r="D68" s="5">
-        <f>D64</f>
-        <v>1423.2075</v>
-      </c>
-      <c r="E68" s="5">
-        <f>E64</f>
-        <v>1779.0093750000001</v>
-      </c>
-      <c r="G68" s="15" t="s">
+        <v>953.72020799999984</v>
+      </c>
+      <c r="J69" s="5">
+        <f t="shared" ref="J69:K69" si="2">D64</f>
+        <v>1108.1320512</v>
+      </c>
+      <c r="K69" s="5">
+        <f t="shared" si="2"/>
+        <v>1329.7584614399998</v>
+      </c>
+      <c r="M69" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H68" s="16"/>
-      <c r="I68" s="5">
-        <f>C63</f>
-        <v>910.8528</v>
-      </c>
-      <c r="J68" s="5">
-        <f t="shared" ref="J68:K68" si="2">D63</f>
-        <v>1093.0233599999999</v>
-      </c>
-      <c r="K68" s="5">
-        <f t="shared" si="2"/>
-        <v>1311.6280319999998</v>
-      </c>
-      <c r="M68" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="N68" s="16"/>
-      <c r="O68" s="5">
-        <f>C65</f>
-        <v>1300.7254</v>
-      </c>
-      <c r="P68" s="5">
-        <f t="shared" ref="P68:Q68" si="3">D65</f>
-        <v>1690.9430200000002</v>
-      </c>
-      <c r="Q68" s="5">
+      <c r="N69" s="16"/>
+      <c r="O69" s="5">
+        <f>C66</f>
+        <v>1380.7700399999999</v>
+      </c>
+      <c r="P69" s="5">
+        <f t="shared" ref="P69:Q69" si="3">D66</f>
+        <v>1693.1097456000002</v>
+      </c>
+      <c r="Q69" s="5">
         <f t="shared" si="3"/>
-        <v>2198.2259260000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A69" s="13" t="s">
+        <v>2116.3871820000004</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A70" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C69" s="3">
-        <f>'DCF &amp; Valuation'!B28</f>
+      <c r="C70" s="3">
+        <f>'DCF &amp; Valuation'!B29</f>
         <v>130.30000000000001</v>
       </c>
-      <c r="D69" s="3">
-        <f>'DCF &amp; Valuation'!B29</f>
+      <c r="D70" s="3">
+        <f>'DCF &amp; Valuation'!B30</f>
         <v>143.19999999999999</v>
       </c>
-      <c r="E69" s="3">
-        <f>'DCF &amp; Valuation'!B30</f>
-        <v>136.30000000000001</v>
-      </c>
-      <c r="G69" s="13" t="s">
+      <c r="E70" s="3">
+        <f>'DCF &amp; Valuation'!B31</f>
+        <v>149.5</v>
+      </c>
+      <c r="G70" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I69" s="3">
-        <f>B28</f>
+      <c r="I70" s="3">
+        <f>B29</f>
         <v>130.30000000000001</v>
       </c>
-      <c r="J69" s="3">
+      <c r="J70" s="3">
+        <f>B30</f>
+        <v>143.19999999999999</v>
+      </c>
+      <c r="K70" s="3">
+        <f>B31</f>
+        <v>149.5</v>
+      </c>
+      <c r="M70" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" s="3">
         <f>B29</f>
+        <v>130.30000000000001</v>
+      </c>
+      <c r="P70" s="3">
+        <f>B30</f>
         <v>143.19999999999999</v>
       </c>
-      <c r="K69" s="3">
-        <f>B30</f>
-        <v>136.30000000000001</v>
-      </c>
-      <c r="M69" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="O69" s="3">
-        <f>B28</f>
-        <v>130.30000000000001</v>
-      </c>
-      <c r="P69" s="3">
-        <f>B29</f>
-        <v>143.19999999999999</v>
-      </c>
-      <c r="Q69" s="3">
-        <f>B30</f>
-        <v>136.30000000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A70" s="15" t="s">
+      <c r="Q70" s="3">
+        <f>B31</f>
+        <v>149.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A71" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B70" s="16"/>
-      <c r="C70" s="5">
-        <f>C68-C69</f>
-        <v>1008.2660000000001</v>
-      </c>
-      <c r="D70" s="5">
-        <f>D68-D69</f>
-        <v>1280.0074999999999</v>
-      </c>
-      <c r="E70" s="5">
-        <f>E68-E69</f>
-        <v>1642.7093750000001</v>
-      </c>
-      <c r="G70" s="15" t="s">
+      <c r="B71" s="16"/>
+      <c r="C71" s="5">
+        <f>C69-C70</f>
+        <v>1030.9547999999993</v>
+      </c>
+      <c r="D71" s="5">
+        <f>D69-D70</f>
+        <v>1250.5601199999987</v>
+      </c>
+      <c r="E71" s="5">
+        <f>E69-E70</f>
+        <v>1582.2653879999984</v>
+      </c>
+      <c r="G71" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H70" s="16"/>
-      <c r="I70" s="5">
-        <f>I68-I69</f>
-        <v>780.55279999999993</v>
-      </c>
-      <c r="J70" s="5">
-        <f>J68-J69</f>
-        <v>949.82335999999987</v>
-      </c>
-      <c r="K70" s="5">
-        <f>K68-K69</f>
-        <v>1175.3280319999999</v>
-      </c>
-      <c r="M70" s="15" t="s">
+      <c r="H71" s="16"/>
+      <c r="I71" s="5">
+        <f>I69-I70</f>
+        <v>823.42020799999977</v>
+      </c>
+      <c r="J71" s="5">
+        <f>J69-J70</f>
+        <v>964.93205119999993</v>
+      </c>
+      <c r="K71" s="5">
+        <f>K69-K70</f>
+        <v>1180.2584614399998</v>
+      </c>
+      <c r="M71" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="N70" s="16"/>
-      <c r="O70" s="5">
-        <f>O68-O69</f>
-        <v>1170.4254000000001</v>
-      </c>
-      <c r="P70" s="5">
-        <f>P68-P69</f>
-        <v>1547.7430200000001</v>
-      </c>
-      <c r="Q70" s="5">
-        <f>Q68-Q69</f>
-        <v>2061.9259259999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A71" s="13" t="s">
+      <c r="N71" s="16"/>
+      <c r="O71" s="5">
+        <f>O69-O70</f>
+        <v>1250.4700399999999</v>
+      </c>
+      <c r="P71" s="5">
+        <f>P69-P70</f>
+        <v>1549.9097456000002</v>
+      </c>
+      <c r="Q71" s="5">
+        <f>Q69-Q70</f>
+        <v>1966.8871820000004</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A72" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C71" s="3">
-        <f>C70*$B$27</f>
-        <v>253.78055219999999</v>
-      </c>
-      <c r="D71" s="3">
-        <f t="shared" ref="D71:E71" si="4">D70*$B$27</f>
-        <v>322.17788774999997</v>
-      </c>
-      <c r="E71" s="3">
+      <c r="C72" s="3">
+        <f>C71*$B$28</f>
+        <v>259.49132315999981</v>
+      </c>
+      <c r="D72" s="3">
+        <f t="shared" ref="D72:E72" si="4">D71*$B$28</f>
+        <v>314.76598220399967</v>
+      </c>
+      <c r="E72" s="3">
         <f t="shared" si="4"/>
-        <v>413.46994968749999</v>
-      </c>
-      <c r="G71" s="13" t="s">
+        <v>398.25619815959959</v>
+      </c>
+      <c r="G72" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="I71" s="3">
-        <f>I70*$B$27</f>
-        <v>196.46513975999997</v>
-      </c>
-      <c r="J71" s="3">
-        <f t="shared" ref="J71:K71" si="5">J70*$B$27</f>
-        <v>239.07053971199994</v>
-      </c>
-      <c r="K71" s="3">
+      <c r="I72" s="3">
+        <f>I71*$B$28</f>
+        <v>207.25486635359994</v>
+      </c>
+      <c r="J72" s="3">
+        <f t="shared" ref="J72:K72" si="5">J71*$B$28</f>
+        <v>242.87339728703995</v>
+      </c>
+      <c r="K72" s="3">
         <f t="shared" si="5"/>
-        <v>295.83006565439996</v>
-      </c>
-      <c r="M71" s="13" t="s">
+        <v>297.07105474444791</v>
+      </c>
+      <c r="M72" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="O71" s="3">
-        <f>O70*$B$27</f>
-        <v>294.59607318000002</v>
-      </c>
-      <c r="P71" s="3">
-        <f t="shared" ref="P71:Q71" si="6">P70*$B$27</f>
-        <v>389.56691813399999</v>
-      </c>
-      <c r="Q71" s="3">
+      <c r="O72" s="3">
+        <f>O71*$B$28</f>
+        <v>314.74330906799997</v>
+      </c>
+      <c r="P72" s="3">
+        <f t="shared" ref="P72:Q72" si="6">P71*$B$28</f>
+        <v>390.11228296752</v>
+      </c>
+      <c r="Q72" s="3">
         <f t="shared" si="6"/>
-        <v>518.98675557419995</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A72" s="17" t="s">
+        <v>495.06550370940005</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A73" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B72" s="16"/>
-      <c r="C72" s="6">
-        <f>C70-C71</f>
-        <v>754.48544780000009</v>
-      </c>
-      <c r="D72" s="6">
-        <f>D70-D71</f>
-        <v>957.82961224999997</v>
-      </c>
-      <c r="E72" s="6">
-        <f>E70-E71</f>
-        <v>1229.2394253125001</v>
-      </c>
-      <c r="G72" s="17" t="s">
+      <c r="B73" s="16"/>
+      <c r="C73" s="6">
+        <f>C71-C72</f>
+        <v>771.46347683999943</v>
+      </c>
+      <c r="D73" s="6">
+        <f>D71-D72</f>
+        <v>935.79413779599906</v>
+      </c>
+      <c r="E73" s="6">
+        <f>E71-E72</f>
+        <v>1184.0091898403989</v>
+      </c>
+      <c r="G73" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H72" s="16"/>
-      <c r="I72" s="6">
-        <f>I70-I71</f>
-        <v>584.08766023999999</v>
-      </c>
-      <c r="J72" s="6">
-        <f>J70-J71</f>
-        <v>710.75282028799995</v>
-      </c>
-      <c r="K72" s="6">
-        <f>K70-K71</f>
-        <v>879.49796634559993</v>
-      </c>
-      <c r="M72" s="17" t="s">
+      <c r="H73" s="16"/>
+      <c r="I73" s="6">
+        <f>I71-I72</f>
+        <v>616.16534164639984</v>
+      </c>
+      <c r="J73" s="6">
+        <f>J71-J72</f>
+        <v>722.05865391295993</v>
+      </c>
+      <c r="K73" s="6">
+        <f>K71-K72</f>
+        <v>883.18740669555189</v>
+      </c>
+      <c r="M73" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="N72" s="16"/>
-      <c r="O72" s="6">
-        <f>O70-O71</f>
-        <v>875.82932682000001</v>
-      </c>
-      <c r="P72" s="6">
-        <f>P70-P71</f>
-        <v>1158.1761018660002</v>
-      </c>
-      <c r="Q72" s="6">
-        <f>Q70-Q71</f>
-        <v>1542.9391704258001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A73" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C73" s="3">
-        <f>C69</f>
-        <v>130.30000000000001</v>
-      </c>
-      <c r="D73" s="3">
-        <f t="shared" ref="D73:E73" si="7">D69</f>
-        <v>143.19999999999999</v>
-      </c>
-      <c r="E73" s="3">
-        <f t="shared" si="7"/>
-        <v>136.30000000000001</v>
-      </c>
-      <c r="G73" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I73" s="3">
-        <f>I69</f>
-        <v>130.30000000000001</v>
-      </c>
-      <c r="J73" s="3">
-        <f t="shared" ref="J73:K73" si="8">J69</f>
-        <v>143.19999999999999</v>
-      </c>
-      <c r="K73" s="3">
-        <f t="shared" si="8"/>
-        <v>136.30000000000001</v>
-      </c>
-      <c r="M73" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="O73" s="3">
-        <f>O69</f>
-        <v>130.30000000000001</v>
-      </c>
-      <c r="P73" s="3">
-        <f t="shared" ref="P73:Q73" si="9">P69</f>
-        <v>143.19999999999999</v>
-      </c>
-      <c r="Q73" s="3">
-        <f t="shared" si="9"/>
-        <v>136.30000000000001</v>
+      <c r="N73" s="16"/>
+      <c r="O73" s="6">
+        <f>O71-O72</f>
+        <v>935.72673093200001</v>
+      </c>
+      <c r="P73" s="6">
+        <f>P71-P72</f>
+        <v>1159.7974626324801</v>
+      </c>
+      <c r="Q73" s="6">
+        <f>Q71-Q72</f>
+        <v>1471.8216782906004</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C74" s="3">
-        <f>('DCF &amp; Valuation'!B31)</f>
-        <v>195</v>
+        <f>C70</f>
+        <v>130.30000000000001</v>
       </c>
       <c r="D74" s="3">
-        <f>('DCF &amp; Valuation'!B32)</f>
-        <v>108.7</v>
+        <f t="shared" ref="D74:E74" si="7">D70</f>
+        <v>143.19999999999999</v>
       </c>
       <c r="E74" s="3">
-        <f>('DCF &amp; Valuation'!B33)</f>
-        <v>135.9</v>
+        <f t="shared" si="7"/>
+        <v>149.5</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I74" s="3">
-        <f>B31</f>
-        <v>195</v>
+        <f>I70</f>
+        <v>130.30000000000001</v>
       </c>
       <c r="J74" s="3">
-        <f>B32</f>
-        <v>108.7</v>
+        <f t="shared" ref="J74:K74" si="8">J70</f>
+        <v>143.19999999999999</v>
       </c>
       <c r="K74" s="3">
-        <f>B33</f>
-        <v>135.9</v>
+        <f t="shared" si="8"/>
+        <v>149.5</v>
       </c>
       <c r="M74" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O74" s="3">
-        <f>B31</f>
-        <v>195</v>
+        <f>O70</f>
+        <v>130.30000000000001</v>
       </c>
       <c r="P74" s="3">
-        <f>B32</f>
-        <v>108.7</v>
+        <f t="shared" ref="P74:Q74" si="9">P70</f>
+        <v>143.19999999999999</v>
       </c>
       <c r="Q74" s="3">
-        <f>B33</f>
-        <v>135.9</v>
+        <f t="shared" si="9"/>
+        <v>149.5</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C75" s="3">
+        <f>('DCF &amp; Valuation'!B32)</f>
+        <v>195</v>
+      </c>
+      <c r="D75" s="3">
+        <f>('DCF &amp; Valuation'!B33)</f>
+        <v>174.4</v>
+      </c>
+      <c r="E75" s="3">
+        <f>('DCF &amp; Valuation'!B34)</f>
+        <v>216.3</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I75" s="3">
+        <f>B32</f>
+        <v>195</v>
+      </c>
+      <c r="J75" s="3">
+        <f>B33</f>
+        <v>174.4</v>
+      </c>
+      <c r="K75" s="3">
+        <f>B34</f>
+        <v>216.3</v>
+      </c>
+      <c r="M75" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="O75" s="3">
+        <f>B32</f>
+        <v>195</v>
+      </c>
+      <c r="P75" s="3">
+        <f>B33</f>
+        <v>174.4</v>
+      </c>
+      <c r="Q75" s="3">
+        <f>B34</f>
+        <v>216.3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A76" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C75" s="3">
-        <f>('DCF &amp; Valuation'!B34)</f>
-        <v>70.599999999999994</v>
-      </c>
-      <c r="D75" s="3">
+      <c r="C76" s="3">
         <f>('DCF &amp; Valuation'!B35)</f>
-        <v>126.4</v>
-      </c>
-      <c r="E75" s="3">
+        <v>346.9</v>
+      </c>
+      <c r="D76" s="3">
         <f>('DCF &amp; Valuation'!B36)</f>
-        <v>46.5</v>
-      </c>
-      <c r="G75" s="13" t="s">
+        <v>475.5</v>
+      </c>
+      <c r="E76" s="3">
+        <f>('DCF &amp; Valuation'!B37)</f>
+        <v>512.6</v>
+      </c>
+      <c r="G76" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I75" s="3">
-        <f>B34</f>
-        <v>70.599999999999994</v>
-      </c>
-      <c r="J75" s="3">
+      <c r="I76" s="3">
         <f>B35</f>
-        <v>126.4</v>
-      </c>
-      <c r="K75" s="3">
+        <v>346.9</v>
+      </c>
+      <c r="J76" s="3">
         <f>B36</f>
-        <v>46.5</v>
-      </c>
-      <c r="M75" s="13" t="s">
+        <v>475.5</v>
+      </c>
+      <c r="K76" s="3">
+        <f>B37</f>
+        <v>512.6</v>
+      </c>
+      <c r="M76" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="O75" s="3">
-        <f>B34</f>
-        <v>70.599999999999994</v>
-      </c>
-      <c r="P75" s="3">
+      <c r="O76" s="3">
         <f>B35</f>
-        <v>126.4</v>
-      </c>
-      <c r="Q75" s="3">
+        <v>346.9</v>
+      </c>
+      <c r="P76" s="3">
         <f>B36</f>
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A76" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B76" s="16"/>
-      <c r="C76" s="6">
-        <f>C72+C73-C74-C75</f>
-        <v>619.18544780000013</v>
-      </c>
-      <c r="D76" s="6">
-        <f>D72+D73-D74-D75</f>
-        <v>865.92961224999988</v>
-      </c>
-      <c r="E76" s="6">
-        <f>E72+E73-E74-E75</f>
-        <v>1183.1394253125</v>
-      </c>
-      <c r="G76" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="H76" s="16"/>
-      <c r="I76" s="6">
-        <f>I72+I73-I74-I75</f>
-        <v>448.78766024000004</v>
-      </c>
-      <c r="J76" s="6">
-        <f>J72+J73-J74-J75</f>
-        <v>618.85282028799986</v>
-      </c>
-      <c r="K76" s="6">
-        <f>K72+K73-K74-K75</f>
-        <v>833.39796634559991</v>
-      </c>
-      <c r="M76" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="N76" s="16"/>
-      <c r="O76" s="6">
-        <f>O72+O73-O74-O75</f>
-        <v>740.52932681999994</v>
-      </c>
-      <c r="P76" s="6">
-        <f>P72+P73-P74-P75</f>
-        <v>1066.2761018660001</v>
-      </c>
-      <c r="Q76" s="6">
-        <f>Q72+Q73-Q74-Q75</f>
-        <v>1496.8391704257999</v>
+        <v>475.5</v>
+      </c>
+      <c r="Q76" s="3">
+        <f>B37</f>
+        <v>512.6</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="17" t="s">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="6">
-        <f>C76/(1+$B$45)^1</f>
-        <v>535.74501811983646</v>
+        <f>C73+C74-C75-C76</f>
+        <v>359.86347683999941</v>
       </c>
       <c r="D77" s="6">
-        <f>D76/(1+$B$45)^2</f>
-        <v>648.27219111567047</v>
+        <f>D73+D74-D75-D76</f>
+        <v>429.09413779599902</v>
       </c>
       <c r="E77" s="6">
-        <f>E76/(1+$B$45)^3</f>
-        <v>766.38699651969546</v>
+        <f>E73+E74-E75-E76</f>
+        <v>604.60918984039893</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="H77" s="16"/>
       <c r="I77" s="6">
-        <f>I76/(1+$B$45)^1</f>
-        <v>388.30976086650497</v>
+        <f>I73+I74-I75-I76</f>
+        <v>204.56534164639982</v>
       </c>
       <c r="J77" s="6">
-        <f>J76/(1+$B$45)^2</f>
-        <v>463.29986653740747</v>
+        <f>J73+J74-J75-J76</f>
+        <v>215.35865391295999</v>
       </c>
       <c r="K77" s="6">
-        <f>K76/(1+$B$45)^3</f>
-        <v>539.83947341161991</v>
+        <f>K73+K74-K75-K76</f>
+        <v>303.78740669555202</v>
       </c>
       <c r="M77" s="17" t="s">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="N77" s="16"/>
       <c r="O77" s="6">
-        <f>O76/(1+$B$45)^1</f>
-        <v>640.73679222448141</v>
+        <f>O73+O74-O75-O76</f>
+        <v>524.12673093199999</v>
       </c>
       <c r="P77" s="6">
-        <f>P76/(1+$B$45)^2</f>
-        <v>798.26019934214105</v>
+        <f>P73+P74-P75-P76</f>
+        <v>653.09746263248007</v>
       </c>
       <c r="Q77" s="6">
-        <f>Q76/(1+$B$45)^3</f>
-        <v>969.58824256292962</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A79" s="66" t="s">
+        <f>Q73+Q74-Q75-Q76</f>
+        <v>892.42167829060043</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A78" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="B78" s="16"/>
+      <c r="C78" s="6">
+        <f>C77/(1+$B$46)^1</f>
+        <v>311.36885662498088</v>
+      </c>
+      <c r="D78" s="6">
+        <f>D77/(1+$B$46)^2</f>
+        <v>321.23834659160747</v>
+      </c>
+      <c r="E78" s="6">
+        <f>E77/(1+$B$46)^3</f>
+        <v>391.63991255519375</v>
+      </c>
+      <c r="G78" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="H78" s="16"/>
+      <c r="I78" s="6">
+        <f>I77/(1+$B$46)^1</f>
+        <v>176.99844700232794</v>
+      </c>
+      <c r="J78" s="6">
+        <f>J77/(1+$B$46)^2</f>
+        <v>161.22676078153253</v>
+      </c>
+      <c r="K78" s="6">
+        <f>K77/(1+$B$46)^3</f>
+        <v>196.78045817500964</v>
+      </c>
+      <c r="M78" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="N78" s="16"/>
+      <c r="O78" s="6">
+        <f>O77/(1+$B$46)^1</f>
+        <v>453.49626022049887</v>
+      </c>
+      <c r="P78" s="6">
+        <f>P77/(1+$B$46)^2</f>
+        <v>488.93688023063987</v>
+      </c>
+      <c r="Q78" s="6">
+        <f>Q77/(1+$B$46)^3</f>
+        <v>578.07250356275767</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A80" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="B79" s="66"/>
-      <c r="C79" s="66"/>
-      <c r="D79" s="66"/>
-    </row>
-    <row r="80" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="11" t="s">
+      <c r="B80" s="68"/>
+      <c r="C80" s="68"/>
+      <c r="D80" s="68"/>
+    </row>
+    <row r="81" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A81" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B81" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C81" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D80" s="11" t="s">
+      <c r="D81" s="11" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B81" s="3">
-        <f>E63</f>
-        <v>1311.6280319999998</v>
-      </c>
-      <c r="C81" s="3">
-        <f>E64</f>
-        <v>1779.0093750000001</v>
-      </c>
-      <c r="D81" s="3">
-        <f>E65</f>
-        <v>2198.2259260000001</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B82" s="3">
-        <f>B81*$B$47</f>
-        <v>13116.280319999998</v>
+        <f>E64</f>
+        <v>1329.7584614399998</v>
       </c>
       <c r="C82" s="3">
-        <f>C81*$B$47</f>
-        <v>17790.09375</v>
+        <f>E65</f>
+        <v>1731.7653879999984</v>
       </c>
       <c r="D82" s="3">
-        <f>D81*$B$47</f>
-        <v>21982.259259999999</v>
+        <f>E66</f>
+        <v>2116.3871820000004</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B83" s="7">
-        <f>B82/(1+$B$45)^3</f>
-        <v>8496.1640740694093</v>
-      </c>
-      <c r="C83" s="7">
-        <f t="shared" ref="C83:D83" si="10">C82/(1+$B$45)^3</f>
-        <v>11523.660039699178</v>
-      </c>
-      <c r="D83" s="7">
-        <f t="shared" si="10"/>
-        <v>14239.165131817768</v>
+        <v>61</v>
+      </c>
+      <c r="B83" s="3">
+        <f>B82*$B$48</f>
+        <v>13297.584614399999</v>
+      </c>
+      <c r="C83" s="3">
+        <f>C82*$B$48</f>
+        <v>17317.653879999983</v>
+      </c>
+      <c r="D83" s="3">
+        <f>D82*$B$48</f>
+        <v>21163.871820000004</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B84" s="7">
+        <f>B83/(1+$B$46)^3</f>
+        <v>8613.6052231585272</v>
+      </c>
+      <c r="C84" s="7">
+        <f t="shared" ref="C84:D84" si="10">C83/(1+$B$46)^3</f>
+        <v>11217.63374621324</v>
+      </c>
+      <c r="D84" s="7">
+        <f t="shared" si="10"/>
+        <v>13709.048833846058</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="3">
-        <f>SUM(I77:K77)</f>
-        <v>1391.4491008155323</v>
-      </c>
-      <c r="C84" s="3">
-        <f>SUM($C$77:$E$77)</f>
-        <v>1950.4042057552024</v>
-      </c>
-      <c r="D84" s="3">
-        <f>SUM(O77:Q77)</f>
-        <v>2408.5852341295522</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="17" t="s">
+      <c r="B85" s="3">
+        <f>SUM(I78:K78)</f>
+        <v>535.00566595887017</v>
+      </c>
+      <c r="C85" s="3">
+        <f>SUM($C$78:$E$78)</f>
+        <v>1024.2471157717821</v>
+      </c>
+      <c r="D85" s="3">
+        <f>SUM(O78:Q78)</f>
+        <v>1520.5056440138965</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B85" s="5">
-        <f>B83+B84</f>
-        <v>9887.6131748849421</v>
-      </c>
-      <c r="C85" s="5">
-        <f>C83+C84</f>
-        <v>13474.064245454381</v>
-      </c>
-      <c r="D85" s="5">
-        <f>D83+D84</f>
-        <v>16647.750365947322</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="13" t="s">
+      <c r="B86" s="5">
+        <f>B84+B85</f>
+        <v>9148.6108891173972</v>
+      </c>
+      <c r="C86" s="5">
+        <f>C84+C85</f>
+        <v>12241.880861985022</v>
+      </c>
+      <c r="D86" s="5">
+        <f>D84+D85</f>
+        <v>15229.554477859954</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B86" s="3">
-        <f>'DCF &amp; Valuation'!$B$11</f>
+      <c r="B87" s="3">
+        <f>'DCF &amp; Valuation'!$B$12</f>
         <v>361.65</v>
       </c>
-      <c r="C86" s="3">
-        <f>'DCF &amp; Valuation'!$B$11</f>
+      <c r="C87" s="3">
+        <f>'DCF &amp; Valuation'!$B$12</f>
         <v>361.65</v>
       </c>
-      <c r="D86" s="3">
-        <f>'DCF &amp; Valuation'!$B$11</f>
+      <c r="D87" s="3">
+        <f>'DCF &amp; Valuation'!$B$12</f>
         <v>361.65</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B87" s="5">
-        <f>B85-B86</f>
-        <v>9525.9631748849424</v>
-      </c>
-      <c r="C87" s="5">
-        <f>C85-C86</f>
-        <v>13112.414245454382</v>
-      </c>
-      <c r="D87" s="5">
-        <f>D85-D86</f>
-        <v>16286.100365947323</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B88" s="5">
+        <f>B86-B87</f>
+        <v>8786.9608891173975</v>
+      </c>
+      <c r="C88" s="5">
+        <f>C86-C87</f>
+        <v>11880.230861985023</v>
+      </c>
+      <c r="D88" s="5">
+        <f>D86-D87</f>
+        <v>14867.904477859955</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B88" s="6">
-        <f>B87/'DCF &amp; Valuation'!$B$6</f>
-        <v>712.08844514183841</v>
-      </c>
-      <c r="C88" s="6">
-        <f>C87/'DCF &amp; Valuation'!$B$6</f>
-        <v>980.18420821935206</v>
-      </c>
-      <c r="D88" s="6">
-        <f>D87/'DCF &amp; Valuation'!$B$6</f>
-        <v>1217.4248077703101</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="13" t="s">
+      <c r="B89" s="6">
+        <f>B88/'DCF &amp; Valuation'!$B$7</f>
+        <v>654.52222637745979</v>
+      </c>
+      <c r="C89" s="6">
+        <f>C88/'DCF &amp; Valuation'!$B$7</f>
+        <v>884.93339754078374</v>
+      </c>
+      <c r="D89" s="6">
+        <f>D88/'DCF &amp; Valuation'!$B$7</f>
+        <v>1107.4789182763466</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="B89" s="3">
-        <f>'DCF &amp; Valuation'!$B$7</f>
-        <v>524</v>
-      </c>
-      <c r="C89" s="3">
-        <f>'DCF &amp; Valuation'!$B$7</f>
-        <v>524</v>
-      </c>
-      <c r="D89" s="3">
-        <f>'DCF &amp; Valuation'!$B$7</f>
-        <v>524</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="17" t="s">
+      <c r="B90" s="3">
+        <f>'DCF &amp; Valuation'!$B$8</f>
+        <v>513</v>
+      </c>
+      <c r="C90" s="3">
+        <f>'DCF &amp; Valuation'!$B$8</f>
+        <v>513</v>
+      </c>
+      <c r="D90" s="3">
+        <f>'DCF &amp; Valuation'!$B$8</f>
+        <v>513</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B90" s="69">
-        <f>B88/B89-1</f>
-        <v>0.3589474143928213</v>
-      </c>
-      <c r="C90" s="69">
-        <f>C88/C89-1</f>
-        <v>0.87058055003693147</v>
-      </c>
-      <c r="D90" s="69">
-        <f>D88/D89-1</f>
-        <v>1.3233297858212025</v>
-      </c>
-      <c r="G90" s="1"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="65" t="s">
+      <c r="B91" s="62">
+        <f>B89/B90-1</f>
+        <v>0.27587178631083775</v>
+      </c>
+      <c r="C91" s="62">
+        <f>C89/C90-1</f>
+        <v>0.72501636947521209</v>
+      </c>
+      <c r="D91" s="62">
+        <f>D89/D90-1</f>
+        <v>1.1588283007336191</v>
+      </c>
+      <c r="G91" s="1"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="66" t="s">
         <v>165</v>
       </c>
-      <c r="B92" s="65"/>
-      <c r="C92" s="65"/>
-      <c r="D92" s="65"/>
-      <c r="E92" s="65"/>
-      <c r="F92" s="65"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="18" t="s">
+      <c r="B93" s="66"/>
+      <c r="C93" s="66"/>
+      <c r="D93" s="66"/>
+      <c r="E93" s="66"/>
+      <c r="F93" s="66"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B94" s="2">
         <v>0.02</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C94" s="2">
         <v>0.03</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D94" s="2">
         <v>0.04</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E94" s="2">
         <v>0.05</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F94" s="2">
         <v>0.06</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="B94" s="3">
-        <f>((E76*(1+0.02)/(0.12-0.02)/(1+0.12)^3)+(C76/(1+0.12)^1+D76/(1+0.12)^2+E76/(1+0.12)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>770.9529431194793</v>
-      </c>
-      <c r="C94" s="3">
-        <f>((E76*(1+0.03)/(0.12-0.03)/(1+0.12)^3)+(C76/(1+0.12)^1+D76/(1+0.12)^2+E76/(1+0.12)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>849.29273473877015</v>
-      </c>
-      <c r="D94" s="3">
-        <f>((E76*(1+0.04)/(0.12-0.04)/(1+0.12)^3)+(C76/(1+0.12)^1+D76/(1+0.12)^2+E76/(1+0.12)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>947.2174742628838</v>
-      </c>
-      <c r="E94" s="3">
-        <f>((E76*(1+0.05)/(0.12-0.05)/(1+0.12)^3)+(C76/(1+0.12)^1+D76/(1+0.12)^2+E76/(1+0.12)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>1073.1207107938872</v>
-      </c>
-      <c r="F94" s="3">
-        <f>((E76*(1+0.06)/(0.12-0.06)/(1+0.12)^3)+(C76/(1+0.12)^1+D76/(1+0.12)^2+E76/(1+0.12)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>1240.9916928352245</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="B95" s="3">
-        <f>((E76*(1+0.02)/(0.13-0.02)/(1+0.13)^3)+(C76/(1+0.13)^1+D76/(1+0.13)^2+E76/(1+0.13)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>694.28748810701484</v>
+        <f>((E77*(1+0.02)/(0.12-0.02)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>381.49983909217798</v>
       </c>
       <c r="C95" s="3">
-        <f>((E76*(1+0.03)/(0.13-0.03)/(1+0.13)^3)+(C76/(1+0.13)^1+D76/(1+0.13)^2+E76/(1+0.13)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>757.25425502584153</v>
+        <f>((E77*(1+0.03)/(0.12-0.03)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>421.39147943580292</v>
       </c>
       <c r="D95" s="3">
-        <f>((E76*(1+0.04)/(0.13-0.04)/(1+0.13)^3)+(C76/(1+0.13)^1+D76/(1+0.13)^2+E76/(1+0.13)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>834.21363681551861</v>
+        <f>((E77*(1+0.04)/(0.12-0.04)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>471.25602986533414</v>
       </c>
       <c r="E95" s="3">
-        <f>((E76*(1+0.05)/(0.13-0.05)/(1+0.13)^3)+(C76/(1+0.13)^1+D76/(1+0.13)^2+E76/(1+0.13)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>930.41286405261485</v>
+        <f>((E77*(1+0.05)/(0.12-0.05)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>535.36759470330276</v>
       </c>
       <c r="F95" s="3">
-        <f>((E76*(1+0.06)/(0.13-0.06)/(1+0.13)^3)+(C76/(1+0.13)^1+D76/(1+0.13)^2+E76/(1+0.13)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>1054.0975847860243</v>
+        <f>((E77*(1+0.06)/(0.12-0.06)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>620.84968115392769</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="B96" s="3">
-        <f>((E76*(1+0.02)/(0.14-0.02)/(1+0.14)^3)+(C76/(1+0.14)^1+D76/(1+0.14)^2+E76/(1+0.14)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>630.48860101971184</v>
+        <f>((E77*(1+0.02)/(0.13-0.02)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>342.44925768004902</v>
       </c>
       <c r="C96" s="3">
-        <f>((E76*(1+0.03)/(0.14-0.03)/(1+0.14)^3)+(C76/(1+0.14)^1+D76/(1+0.14)^2+E76/(1+0.14)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>682.04437759112466</v>
+        <f>((E77*(1+0.03)/(0.13-0.03)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>374.51275399024553</v>
       </c>
       <c r="D96" s="3">
-        <f>((E76*(1+0.04)/(0.14-0.04)/(1+0.14)^3)+(C76/(1+0.14)^1+D76/(1+0.14)^2+E76/(1+0.14)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>743.91130947681984</v>
+        <f>((E77*(1+0.04)/(0.13-0.04)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>413.70147170270798</v>
       </c>
       <c r="E96" s="3">
-        <f>((E76*(1+0.05)/(0.14-0.05)/(1+0.14)^3)+(C76/(1+0.14)^1+D76/(1+0.14)^2+E76/(1+0.14)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>819.52644844822544</v>
+        <f>((E77*(1+0.05)/(0.13-0.05)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>462.68736884328587</v>
       </c>
       <c r="F96" s="3">
-        <f>((E76*(1+0.06)/(0.14-0.06)/(1+0.14)^3)+(C76/(1+0.14)^1+D76/(1+0.14)^2+E76/(1+0.14)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>914.04537216248207</v>
+        <f>((E77*(1+0.06)/(0.13-0.06)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>525.66923659545728</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="B97" s="3">
-        <f>((E76*(1+0.02)/(0.15-0.02)/(1+0.15)^3)+(C76/(1+0.15)^1+D76/(1+0.15)^2+E76/(1+0.15)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>576.58438867134566</v>
+        <f>((E77*(1+0.02)/(0.14-0.02)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>309.95058079639762</v>
       </c>
       <c r="C97" s="3">
-        <f>((E76*(1+0.03)/(0.15-0.03)/(1+0.15)^3)+(C76/(1+0.15)^1+D76/(1+0.15)^2+E76/(1+0.15)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>619.45312559467209</v>
-      </c>
-      <c r="D97" s="10">
-        <f>((E76*(1+0.04)/(0.15-0.04)/(1+0.15)^3)+(C76/(1+0.15)^1+D76/(1+0.15)^2+E76/(1+0.15)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>670.11617832223953</v>
+        <f>((E77*(1+0.03)/(0.14-0.03)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>336.20345247389446</v>
+      </c>
+      <c r="D97" s="3">
+        <f>((E77*(1+0.04)/(0.14-0.04)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>367.70689848689079</v>
       </c>
       <c r="E97" s="3">
-        <f>((E76*(1+0.05)/(0.15-0.05)/(1+0.15)^3)+(C76/(1+0.15)^1+D76/(1+0.15)^2+E76/(1+0.15)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>730.91184159532065</v>
+        <f>((E77*(1+0.05)/(0.14-0.05)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>406.21111028055265</v>
       </c>
       <c r="F97" s="3">
-        <f>((E76*(1+0.06)/(0.15-0.06)/(1+0.15)^3)+(C76/(1+0.15)^1+D76/(1+0.15)^2+E76/(1+0.15)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>805.21765226241973</v>
+        <f>((E77*(1+0.06)/(0.14-0.06)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>454.34137502263019</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="B98" s="3">
-        <f>((E76*(1+0.02)/(0.16-0.02)/(1+0.16)^3)+(C76/(1+0.16)^1+D76/(1+0.16)^2+E76/(1+0.16)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>530.4521734070446</v>
+        <f>((E77*(1+0.02)/(0.15-0.02)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>282.49048282722947</v>
       </c>
       <c r="C98" s="3">
-        <f>((E76*(1+0.03)/(0.16-0.03)/(1+0.16)^3)+(C76/(1+0.16)^1+D76/(1+0.16)^2+E76/(1+0.16)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>566.56600764844472</v>
-      </c>
-      <c r="D98" s="3">
-        <f>((E76*(1+0.04)/(0.16-0.04)/(1+0.16)^3)+(C76/(1+0.16)^1+D76/(1+0.16)^2+E76/(1+0.16)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>608.69881426341135</v>
+        <f>((E77*(1+0.03)/(0.15-0.03)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>304.31980098065821</v>
+      </c>
+      <c r="D98" s="10">
+        <f>((E77*(1+0.04)/(0.15-0.04)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>330.11808607107406</v>
       </c>
       <c r="E98" s="3">
-        <f>((E76*(1+0.05)/(0.16-0.05)/(1+0.16)^3)+(C76/(1+0.16)^1+D76/(1+0.16)^2+E76/(1+0.16)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>658.49213117200838</v>
+        <f>((E77*(1+0.05)/(0.15-0.05)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>361.07602817957297</v>
       </c>
       <c r="F98" s="3">
-        <f>((E76*(1+0.06)/(0.16-0.06)/(1+0.16)^3)+(C76/(1+0.16)^1+D76/(1+0.16)^2+E76/(1+0.16)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>718.24411146232455</v>
+        <f>((E77*(1+0.06)/(0.15-0.06)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>398.91351297884944</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="B99" s="3">
+        <f>((E77*(1+0.02)/(0.16-0.02)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>258.98806960427538</v>
+      </c>
+      <c r="C99" s="3">
+        <f>((E77*(1+0.03)/(0.16-0.03)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>277.3777034954187</v>
+      </c>
+      <c r="D99" s="3">
+        <f>((E77*(1+0.04)/(0.16-0.04)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>298.83227636841923</v>
+      </c>
+      <c r="E99" s="3">
+        <f>((E77*(1+0.05)/(0.16-0.05)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>324.18768067287442</v>
+      </c>
+      <c r="F99" s="3">
+        <f>((E77*(1+0.06)/(0.16-0.06)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>354.61416583822069</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
         <v>0.17</v>
       </c>
-      <c r="B99" s="3">
-        <f>((E76*(1+0.02)/(0.17-0.02)/(1+0.17)^3)+(C76/(1+0.17)^1+D76/(1+0.17)^2+E76/(1+0.17)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>490.53541646288136</v>
-      </c>
-      <c r="C99" s="3">
-        <f>((E76*(1+0.03)/(0.17-0.03)/(1+0.17)^3)+(C76/(1+0.17)^1+D76/(1+0.17)^2+E76/(1+0.17)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>521.30133944814736</v>
-      </c>
-      <c r="D99" s="3">
-        <f>((E76*(1+0.04)/(0.17-0.04)/(1+0.17)^3)+(C76/(1+0.17)^1+D76/(1+0.17)^2+E76/(1+0.17)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>556.80048135422373</v>
-      </c>
-      <c r="E99" s="3">
-        <f>((E76*(1+0.05)/(0.17-0.05)/(1+0.17)^3)+(C76/(1+0.17)^1+D76/(1+0.17)^2+E76/(1+0.17)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>598.21614691131265</v>
-      </c>
-      <c r="F99" s="3">
-        <f>((E76*(1+0.06)/(0.17-0.06)/(1+0.17)^3)+(C76/(1+0.17)^1+D76/(1+0.17)^2+E76/(1+0.17)^3)-'DCF &amp; Valuation'!B11)/'DCF &amp; Valuation'!B6</f>
-        <v>647.16193347878152</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A115" s="64"/>
-      <c r="B115" s="64"/>
-      <c r="C115" s="64"/>
-      <c r="D115" s="64"/>
-      <c r="E115" s="64"/>
-      <c r="F115" s="64"/>
-      <c r="G115" s="64"/>
-      <c r="H115" s="64"/>
-      <c r="I115" s="64"/>
+      <c r="B100" s="3">
+        <f>((E77*(1+0.02)/(0.17-0.02)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>238.65073211024</v>
+      </c>
+      <c r="C100" s="3">
+        <f>((E77*(1+0.03)/(0.17-0.03)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>254.31714006460689</v>
+      </c>
+      <c r="D100" s="3">
+        <f>((E77*(1+0.04)/(0.17-0.04)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>272.39376462733787</v>
+      </c>
+      <c r="E100" s="3">
+        <f>((E77*(1+0.05)/(0.17-0.05)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>293.48315995052405</v>
+      </c>
+      <c r="F100" s="3">
+        <f>((E77*(1+0.06)/(0.17-0.06)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
+        <v>318.40699078701675</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A116" s="67"/>
+      <c r="B116" s="67"/>
+      <c r="C116" s="67"/>
+      <c r="D116" s="67"/>
+      <c r="E116" s="67"/>
+      <c r="F116" s="67"/>
+      <c r="G116" s="67"/>
+      <c r="H116" s="67"/>
+      <c r="I116" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="M67:N67"/>
-    <mergeCell ref="A115:I115"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="M68:N68"/>
+    <mergeCell ref="A116:I116"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C38:C47"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A79:D79"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C39:C48"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="G68:H68"/>
   </mergeCells>
-  <conditionalFormatting sqref="B94:F99">
+  <conditionalFormatting sqref="B95:F100">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>$B$8</formula>
+    </cfRule>
     <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>$B$7</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>$B$7</formula>
+      <formula>$B$8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3106,10 +3119,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="67"/>
+      <c r="B1" s="70"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
@@ -3143,20 +3156,20 @@
       <c r="B6" s="20">
         <v>4.24E-2</v>
       </c>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="70" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="67"/>
-      <c r="G6" s="67" t="s">
+      <c r="E6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="H6" s="67" t="s">
+      <c r="H6" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="J6" s="67" t="s">
+      <c r="J6" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="K6" s="67"/>
+      <c r="K6" s="70"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
@@ -3240,10 +3253,10 @@
       <c r="B10" s="37">
         <v>8.556597674634385E-2</v>
       </c>
-      <c r="D10" s="67" t="s">
+      <c r="D10" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="E10" s="67"/>
+      <c r="E10" s="70"/>
       <c r="G10" s="19" t="s">
         <v>80</v>
       </c>
@@ -3404,7 +3417,7 @@
       <c r="A18" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="72">
+      <c r="B18" s="64">
         <f>B15*(1+(1-B17)*B16)</f>
         <v>1.3044376921972554</v>
       </c>
@@ -3724,12 +3737,12 @@
         <f>SLOPE(Q3:Q127,$C$3:$C$127)</f>
         <v>1.6458369435020117</v>
       </c>
-      <c r="U3" s="62" t="s">
+      <c r="U3" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="V3" s="62"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
+      <c r="X3" s="71"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="60">
@@ -3794,13 +3807,13 @@
       <c r="S4" s="56">
         <v>0.16</v>
       </c>
-      <c r="U4" s="63">
+      <c r="U4" s="72">
         <f>(G6*G8)+(K6*K8)+(O6*O8)+(S6*S8)</f>
         <v>1.0652906044126578</v>
       </c>
-      <c r="V4" s="63"/>
-      <c r="W4" s="63"/>
-      <c r="X4" s="63"/>
+      <c r="V4" s="72"/>
+      <c r="W4" s="72"/>
+      <c r="X4" s="72"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="60">

--- a/Transrail_DCF.xlsx
+++ b/Transrail_DCF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jimit\Desktop\Avalon Research\Company\Transrail Lighting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7497BA8-4598-465B-9EBA-BEE522B54CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B308762-9B9A-49E6-A369-E350D06E4035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1491,7 +1491,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="38">
-        <v>842.79</v>
+        <v>787.8</v>
       </c>
       <c r="C10" s="63" t="s">
         <v>115</v>
@@ -1502,7 +1502,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="38">
-        <v>481.14</v>
+        <v>636.6</v>
       </c>
       <c r="C11" s="63" t="s">
         <v>9</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B12" s="13">
         <f>B10-B11</f>
-        <v>361.65</v>
+        <v>151.19999999999993</v>
       </c>
       <c r="C12" s="63" t="s">
         <v>116</v>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B13" s="13">
         <f>B9+B12</f>
-        <v>7248.6750000000002</v>
+        <v>7038.2250000000004</v>
       </c>
       <c r="C13" s="63" t="s">
         <v>117</v>
@@ -2797,15 +2797,15 @@
       </c>
       <c r="B87" s="3">
         <f>'DCF &amp; Valuation'!$B$12</f>
-        <v>361.65</v>
+        <v>151.19999999999993</v>
       </c>
       <c r="C87" s="3">
         <f>'DCF &amp; Valuation'!$B$12</f>
-        <v>361.65</v>
+        <v>151.19999999999993</v>
       </c>
       <c r="D87" s="3">
         <f>'DCF &amp; Valuation'!$B$12</f>
-        <v>361.65</v>
+        <v>151.19999999999993</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -2814,15 +2814,15 @@
       </c>
       <c r="B88" s="5">
         <f>B86-B87</f>
-        <v>8786.9608891173975</v>
+        <v>8997.4108891173964</v>
       </c>
       <c r="C88" s="5">
         <f>C86-C87</f>
-        <v>11880.230861985023</v>
+        <v>12090.680861985022</v>
       </c>
       <c r="D88" s="5">
         <f>D86-D87</f>
-        <v>14867.904477859955</v>
+        <v>15078.354477859953</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -2831,15 +2831,15 @@
       </c>
       <c r="B89" s="6">
         <f>B88/'DCF &amp; Valuation'!$B$7</f>
-        <v>654.52222637745979</v>
+        <v>670.198204031091</v>
       </c>
       <c r="C89" s="6">
         <f>C88/'DCF &amp; Valuation'!$B$7</f>
-        <v>884.93339754078374</v>
+        <v>900.60937519441495</v>
       </c>
       <c r="D89" s="6">
         <f>D88/'DCF &amp; Valuation'!$B$7</f>
-        <v>1107.4789182763466</v>
+        <v>1123.1548959299778</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -2865,15 +2865,15 @@
       </c>
       <c r="B91" s="62">
         <f>B89/B90-1</f>
-        <v>0.27587178631083775</v>
+        <v>0.30642924762395896</v>
       </c>
       <c r="C91" s="62">
         <f>C89/C90-1</f>
-        <v>0.72501636947521209</v>
+        <v>0.75557383078833329</v>
       </c>
       <c r="D91" s="62">
         <f>D89/D90-1</f>
-        <v>1.1588283007336191</v>
+        <v>1.1893857620467405</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -2913,23 +2913,23 @@
       </c>
       <c r="B95" s="3">
         <f>((E77*(1+0.02)/(0.12-0.02)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>381.49983909217798</v>
+        <v>397.17581674580924</v>
       </c>
       <c r="C95" s="3">
         <f>((E77*(1+0.03)/(0.12-0.03)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>421.39147943580292</v>
+        <v>437.06745708943419</v>
       </c>
       <c r="D95" s="3">
         <f>((E77*(1+0.04)/(0.12-0.04)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>471.25602986533414</v>
+        <v>486.93200751896541</v>
       </c>
       <c r="E95" s="3">
         <f>((E77*(1+0.05)/(0.12-0.05)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>535.36759470330276</v>
+        <v>551.04357235693396</v>
       </c>
       <c r="F95" s="3">
         <f>((E77*(1+0.06)/(0.12-0.06)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>620.84968115392769</v>
+        <v>636.5256588075589</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
@@ -2938,23 +2938,23 @@
       </c>
       <c r="B96" s="3">
         <f>((E77*(1+0.02)/(0.13-0.02)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>342.44925768004902</v>
+        <v>358.12523533368028</v>
       </c>
       <c r="C96" s="3">
         <f>((E77*(1+0.03)/(0.13-0.03)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>374.51275399024553</v>
+        <v>390.18873164387679</v>
       </c>
       <c r="D96" s="3">
         <f>((E77*(1+0.04)/(0.13-0.04)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>413.70147170270798</v>
+        <v>429.37744935633924</v>
       </c>
       <c r="E96" s="3">
         <f>((E77*(1+0.05)/(0.13-0.05)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>462.68736884328587</v>
+        <v>478.36334649691713</v>
       </c>
       <c r="F96" s="3">
         <f>((E77*(1+0.06)/(0.13-0.06)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>525.66923659545728</v>
+        <v>541.3452142490886</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -2963,23 +2963,23 @@
       </c>
       <c r="B97" s="3">
         <f>((E77*(1+0.02)/(0.14-0.02)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>309.95058079639762</v>
+        <v>325.62655845002894</v>
       </c>
       <c r="C97" s="3">
         <f>((E77*(1+0.03)/(0.14-0.03)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>336.20345247389446</v>
+        <v>351.87943012752572</v>
       </c>
       <c r="D97" s="3">
         <f>((E77*(1+0.04)/(0.14-0.04)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>367.70689848689079</v>
+        <v>383.38287614052206</v>
       </c>
       <c r="E97" s="3">
         <f>((E77*(1+0.05)/(0.14-0.05)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>406.21111028055265</v>
+        <v>421.88708793418397</v>
       </c>
       <c r="F97" s="3">
         <f>((E77*(1+0.06)/(0.14-0.06)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>454.34137502263019</v>
+        <v>470.01735267626145</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -2988,23 +2988,23 @@
       </c>
       <c r="B98" s="3">
         <f>((E77*(1+0.02)/(0.15-0.02)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>282.49048282722947</v>
+        <v>298.16646048086079</v>
       </c>
       <c r="C98" s="3">
         <f>((E77*(1+0.03)/(0.15-0.03)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>304.31980098065821</v>
+        <v>319.99577863428954</v>
       </c>
       <c r="D98" s="10">
         <f>((E77*(1+0.04)/(0.15-0.04)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>330.11808607107406</v>
+        <v>345.79406372470538</v>
       </c>
       <c r="E98" s="3">
         <f>((E77*(1+0.05)/(0.15-0.05)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>361.07602817957297</v>
+        <v>376.75200583320424</v>
       </c>
       <c r="F98" s="3">
         <f>((E77*(1+0.06)/(0.15-0.06)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>398.91351297884944</v>
+        <v>414.5894906324807</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
@@ -3013,23 +3013,23 @@
       </c>
       <c r="B99" s="3">
         <f>((E77*(1+0.02)/(0.16-0.02)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>258.98806960427538</v>
+        <v>274.6640472579067</v>
       </c>
       <c r="C99" s="3">
         <f>((E77*(1+0.03)/(0.16-0.03)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>277.3777034954187</v>
+        <v>293.05368114905002</v>
       </c>
       <c r="D99" s="3">
         <f>((E77*(1+0.04)/(0.16-0.04)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>298.83227636841923</v>
+        <v>314.50825402205055</v>
       </c>
       <c r="E99" s="3">
         <f>((E77*(1+0.05)/(0.16-0.05)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>324.18768067287442</v>
+        <v>339.86365832650569</v>
       </c>
       <c r="F99" s="3">
         <f>((E77*(1+0.06)/(0.16-0.06)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>354.61416583822069</v>
+        <v>370.29014349185195</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -3038,23 +3038,23 @@
       </c>
       <c r="B100" s="3">
         <f>((E77*(1+0.02)/(0.17-0.02)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>238.65073211024</v>
+        <v>254.32670976387129</v>
       </c>
       <c r="C100" s="3">
         <f>((E77*(1+0.03)/(0.17-0.03)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>254.31714006460689</v>
+        <v>269.99311771823818</v>
       </c>
       <c r="D100" s="3">
         <f>((E77*(1+0.04)/(0.17-0.04)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>272.39376462733787</v>
+        <v>288.06974228096919</v>
       </c>
       <c r="E100" s="3">
         <f>((E77*(1+0.05)/(0.17-0.05)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>293.48315995052405</v>
+        <v>309.15913760415532</v>
       </c>
       <c r="F100" s="3">
         <f>((E77*(1+0.06)/(0.17-0.06)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>318.40699078701675</v>
+        <v>334.08296844064802</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">

--- a/Transrail_DCF.xlsx
+++ b/Transrail_DCF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jimit\Desktop\Avalon Research\Company\Transrail Lighting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B308762-9B9A-49E6-A369-E350D06E4035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93FD3918-2E09-49D1-B02C-6D3084807D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1470,7 +1470,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="38">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="C8" s="63" t="s">
         <v>6</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B9" s="13">
         <f>B8*B7</f>
-        <v>6887.0250000000005</v>
+        <v>6564.8250000000007</v>
       </c>
       <c r="C9" s="63"/>
     </row>
@@ -1491,7 +1491,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="38">
-        <v>787.8</v>
+        <v>659</v>
       </c>
       <c r="C10" s="63" t="s">
         <v>115</v>
@@ -1502,7 +1502,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="38">
-        <v>636.6</v>
+        <v>842</v>
       </c>
       <c r="C11" s="63" t="s">
         <v>9</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B12" s="13">
         <f>B10-B11</f>
-        <v>151.19999999999993</v>
+        <v>-183</v>
       </c>
       <c r="C12" s="63" t="s">
         <v>116</v>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B13" s="13">
         <f>B9+B12</f>
-        <v>7038.2250000000004</v>
+        <v>6381.8250000000007</v>
       </c>
       <c r="C13" s="63" t="s">
         <v>117</v>
@@ -1575,7 +1575,7 @@
         <v>167</v>
       </c>
       <c r="B19" s="41">
-        <v>7325.0399999999991</v>
+        <v>6879.2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1583,10 +1583,10 @@
         <v>130</v>
       </c>
       <c r="C20" s="42">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="D20" s="42">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="E20" s="42">
         <v>0.2</v>
@@ -1597,13 +1597,13 @@
         <v>131</v>
       </c>
       <c r="C21" s="42">
-        <v>0.27</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="D21" s="42">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="E21" s="42">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1611,10 +1611,10 @@
         <v>132</v>
       </c>
       <c r="C22" s="42">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="D22" s="42">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="E22" s="42">
         <v>0.25</v>
@@ -1634,7 +1634,7 @@
         <v>20</v>
       </c>
       <c r="C24" s="42">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="D24" s="42">
         <v>0.1</v>
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="C25" s="42">
-        <v>0.12482851401053319</v>
+        <v>0.114</v>
       </c>
       <c r="D25" s="42">
-        <v>0.11985724729266471</v>
+        <v>0.115</v>
       </c>
       <c r="E25" s="42">
-        <v>0.12010017373026666</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1662,13 +1662,13 @@
         <v>22</v>
       </c>
       <c r="C26" s="42">
-        <v>0.14499999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="D26" s="42">
-        <v>0.14000000000000001</v>
+        <v>0.125</v>
       </c>
       <c r="E26" s="42">
-        <v>0.14000000000000001</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1691,7 +1691,7 @@
         <v>140</v>
       </c>
       <c r="B29" s="41">
-        <v>130.30000000000001</v>
+        <v>78.599999999999994</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1699,7 +1699,7 @@
         <v>141</v>
       </c>
       <c r="B30" s="41">
-        <v>143.19999999999999</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1707,7 +1707,7 @@
         <v>142</v>
       </c>
       <c r="B31" s="41">
-        <v>149.5</v>
+        <v>143.30000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1715,7 +1715,7 @@
         <v>143</v>
       </c>
       <c r="B32" s="41">
-        <v>195</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1723,7 +1723,7 @@
         <v>144</v>
       </c>
       <c r="B33" s="41">
-        <v>174.4</v>
+        <v>375</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1731,7 +1731,7 @@
         <v>145</v>
       </c>
       <c r="B34" s="41">
-        <v>216.3</v>
+        <v>192.8</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1739,7 +1739,7 @@
         <v>146</v>
       </c>
       <c r="B35" s="41">
-        <v>346.9</v>
+        <v>186.5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1747,7 +1747,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="41">
-        <v>475.5</v>
+        <v>337.2</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1755,7 +1755,7 @@
         <v>148</v>
       </c>
       <c r="B37" s="41">
-        <v>512.6</v>
+        <v>471.3</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1933,11 +1933,11 @@
       </c>
       <c r="C53" s="8">
         <f>'DCF &amp; Valuation'!C20</f>
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="D53" s="8">
         <f>'DCF &amp; Valuation'!D20</f>
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="E53" s="8">
         <f>'DCF &amp; Valuation'!E20</f>
@@ -1950,15 +1950,15 @@
       </c>
       <c r="C54" s="9">
         <f>'DCF &amp; Valuation'!C21</f>
-        <v>0.27</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="D54" s="9">
         <f>'DCF &amp; Valuation'!D21</f>
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="E54" s="9">
         <f>'DCF &amp; Valuation'!E21</f>
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1967,11 +1967,11 @@
       </c>
       <c r="C55" s="8">
         <f>'DCF &amp; Valuation'!C22</f>
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="D55" s="8">
         <f>'DCF &amp; Valuation'!D22</f>
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="E55" s="8">
         <f>'DCF &amp; Valuation'!E22</f>
@@ -1984,19 +1984,19 @@
       </c>
       <c r="B56" s="3">
         <f>'DCF &amp; Valuation'!B19</f>
-        <v>7325.0399999999991</v>
+        <v>6879.2</v>
       </c>
       <c r="C56" s="3">
         <f t="shared" ref="C56:E58" si="0">B56*(1+C53)</f>
-        <v>9083.0495999999985</v>
+        <v>8255.0399999999991</v>
       </c>
       <c r="D56" s="3">
         <f t="shared" si="0"/>
-        <v>11081.320511999998</v>
+        <v>9906.0479999999989</v>
       </c>
       <c r="E56" s="3">
         <f t="shared" si="0"/>
-        <v>13297.584614399997</v>
+        <v>11887.257599999999</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -2005,19 +2005,19 @@
       </c>
       <c r="B57" s="10">
         <f>'DCF &amp; Valuation'!B19</f>
-        <v>7325.0399999999991</v>
+        <v>6879.2</v>
       </c>
       <c r="C57" s="10">
         <f t="shared" si="0"/>
-        <v>9302.8007999999991</v>
+        <v>8495.8119999999981</v>
       </c>
       <c r="D57" s="10">
         <f t="shared" si="0"/>
-        <v>11628.500999999998</v>
+        <v>10449.848759999997</v>
       </c>
       <c r="E57" s="10">
         <f t="shared" si="0"/>
-        <v>14419.341239999998</v>
+        <v>12853.313974799996</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="B58" s="3">
         <f>'DCF &amp; Valuation'!B19</f>
-        <v>7325.0399999999991</v>
+        <v>6879.2</v>
       </c>
       <c r="C58" s="3">
         <f t="shared" si="0"/>
-        <v>9522.5519999999997</v>
+        <v>8599</v>
       </c>
       <c r="D58" s="3">
         <f t="shared" si="0"/>
-        <v>12093.64104</v>
+        <v>10748.75</v>
       </c>
       <c r="E58" s="3">
         <f t="shared" si="0"/>
-        <v>15117.051300000001</v>
+        <v>13435.9375</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="C61" s="8">
         <f>'DCF &amp; Valuation'!C24</f>
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="D61" s="8">
         <f>'DCF &amp; Valuation'!D24</f>
@@ -2079,15 +2079,15 @@
       </c>
       <c r="C62" s="9">
         <f>'DCF &amp; Valuation'!C25</f>
-        <v>0.12482851401053319</v>
+        <v>0.114</v>
       </c>
       <c r="D62" s="9">
         <f>'DCF &amp; Valuation'!D25</f>
-        <v>0.11985724729266471</v>
+        <v>0.115</v>
       </c>
       <c r="E62" s="9">
         <f>'DCF &amp; Valuation'!E25</f>
-        <v>0.12010017373026666</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -2096,15 +2096,15 @@
       </c>
       <c r="C63" s="8">
         <f>'DCF &amp; Valuation'!C26</f>
-        <v>0.14499999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="D63" s="8">
         <f>'DCF &amp; Valuation'!D26</f>
-        <v>0.14000000000000001</v>
+        <v>0.125</v>
       </c>
       <c r="E63" s="8">
         <f>'DCF &amp; Valuation'!E26</f>
-        <v>0.14000000000000001</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -2113,15 +2113,15 @@
       </c>
       <c r="C64" s="3">
         <f t="shared" ref="C64:E66" si="1">C56*C61</f>
-        <v>953.72020799999984</v>
+        <v>825.50399999999991</v>
       </c>
       <c r="D64" s="3">
         <f t="shared" si="1"/>
-        <v>1108.1320512</v>
+        <v>990.60479999999995</v>
       </c>
       <c r="E64" s="3">
         <f t="shared" si="1"/>
-        <v>1329.7584614399998</v>
+        <v>1188.72576</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.3">
@@ -2130,15 +2130,15 @@
       </c>
       <c r="C65" s="10">
         <f t="shared" si="1"/>
-        <v>1161.2547999999992</v>
+        <v>968.52256799999986</v>
       </c>
       <c r="D65" s="10">
         <f t="shared" si="1"/>
-        <v>1393.7601199999988</v>
+        <v>1201.7326073999998</v>
       </c>
       <c r="E65" s="10">
         <f t="shared" si="1"/>
-        <v>1731.7653879999984</v>
+        <v>1478.1311071019995</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.3">
@@ -2147,15 +2147,15 @@
       </c>
       <c r="C66" s="3">
         <f t="shared" si="1"/>
-        <v>1380.7700399999999</v>
+        <v>1074.875</v>
       </c>
       <c r="D66" s="3">
         <f t="shared" si="1"/>
-        <v>1693.1097456000002</v>
+        <v>1343.59375</v>
       </c>
       <c r="E66" s="3">
         <f t="shared" si="1"/>
-        <v>2116.3871820000004</v>
+        <v>1679.4921875</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.3">
@@ -2206,15 +2206,15 @@
       <c r="B69" s="16"/>
       <c r="C69" s="5">
         <f>C65</f>
-        <v>1161.2547999999992</v>
+        <v>968.52256799999986</v>
       </c>
       <c r="D69" s="5">
         <f>D65</f>
-        <v>1393.7601199999988</v>
+        <v>1201.7326073999998</v>
       </c>
       <c r="E69" s="5">
         <f>E65</f>
-        <v>1731.7653879999984</v>
+        <v>1478.1311071019995</v>
       </c>
       <c r="G69" s="15" t="s">
         <v>36</v>
@@ -2222,15 +2222,15 @@
       <c r="H69" s="16"/>
       <c r="I69" s="5">
         <f>C64</f>
-        <v>953.72020799999984</v>
+        <v>825.50399999999991</v>
       </c>
       <c r="J69" s="5">
         <f t="shared" ref="J69:K69" si="2">D64</f>
-        <v>1108.1320512</v>
+        <v>990.60479999999995</v>
       </c>
       <c r="K69" s="5">
         <f t="shared" si="2"/>
-        <v>1329.7584614399998</v>
+        <v>1188.72576</v>
       </c>
       <c r="M69" s="15" t="s">
         <v>36</v>
@@ -2238,15 +2238,15 @@
       <c r="N69" s="16"/>
       <c r="O69" s="5">
         <f>C66</f>
-        <v>1380.7700399999999</v>
+        <v>1074.875</v>
       </c>
       <c r="P69" s="5">
         <f t="shared" ref="P69:Q69" si="3">D66</f>
-        <v>1693.1097456000002</v>
+        <v>1343.59375</v>
       </c>
       <c r="Q69" s="5">
         <f t="shared" si="3"/>
-        <v>2116.3871820000004</v>
+        <v>1679.4921875</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.3">
@@ -2255,45 +2255,45 @@
       </c>
       <c r="C70" s="3">
         <f>'DCF &amp; Valuation'!B29</f>
-        <v>130.30000000000001</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="D70" s="3">
         <f>'DCF &amp; Valuation'!B30</f>
-        <v>143.19999999999999</v>
+        <v>107.1</v>
       </c>
       <c r="E70" s="3">
         <f>'DCF &amp; Valuation'!B31</f>
-        <v>149.5</v>
+        <v>143.30000000000001</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I70" s="3">
         <f>B29</f>
-        <v>130.30000000000001</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="J70" s="3">
         <f>B30</f>
-        <v>143.19999999999999</v>
+        <v>107.1</v>
       </c>
       <c r="K70" s="3">
         <f>B31</f>
-        <v>149.5</v>
+        <v>143.30000000000001</v>
       </c>
       <c r="M70" s="13" t="s">
         <v>37</v>
       </c>
       <c r="O70" s="3">
         <f>B29</f>
-        <v>130.30000000000001</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="P70" s="3">
         <f>B30</f>
-        <v>143.19999999999999</v>
+        <v>107.1</v>
       </c>
       <c r="Q70" s="3">
         <f>B31</f>
-        <v>149.5</v>
+        <v>143.30000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.3">
@@ -2303,15 +2303,15 @@
       <c r="B71" s="16"/>
       <c r="C71" s="5">
         <f>C69-C70</f>
-        <v>1030.9547999999993</v>
+        <v>889.92256799999984</v>
       </c>
       <c r="D71" s="5">
         <f>D69-D70</f>
-        <v>1250.5601199999987</v>
+        <v>1094.6326073999999</v>
       </c>
       <c r="E71" s="5">
         <f>E69-E70</f>
-        <v>1582.2653879999984</v>
+        <v>1334.8311071019996</v>
       </c>
       <c r="G71" s="15" t="s">
         <v>38</v>
@@ -2319,15 +2319,15 @@
       <c r="H71" s="16"/>
       <c r="I71" s="5">
         <f>I69-I70</f>
-        <v>823.42020799999977</v>
+        <v>746.90399999999988</v>
       </c>
       <c r="J71" s="5">
         <f>J69-J70</f>
-        <v>964.93205119999993</v>
+        <v>883.50479999999993</v>
       </c>
       <c r="K71" s="5">
         <f>K69-K70</f>
-        <v>1180.2584614399998</v>
+        <v>1045.4257600000001</v>
       </c>
       <c r="M71" s="15" t="s">
         <v>38</v>
@@ -2335,15 +2335,15 @@
       <c r="N71" s="16"/>
       <c r="O71" s="5">
         <f>O69-O70</f>
-        <v>1250.4700399999999</v>
+        <v>996.27499999999998</v>
       </c>
       <c r="P71" s="5">
         <f>P69-P70</f>
-        <v>1549.9097456000002</v>
+        <v>1236.4937500000001</v>
       </c>
       <c r="Q71" s="5">
         <f>Q69-Q70</f>
-        <v>1966.8871820000004</v>
+        <v>1536.1921875</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.3">
@@ -2352,45 +2352,45 @@
       </c>
       <c r="C72" s="3">
         <f>C71*$B$28</f>
-        <v>259.49132315999981</v>
+        <v>223.99351036559995</v>
       </c>
       <c r="D72" s="3">
         <f t="shared" ref="D72:E72" si="4">D71*$B$28</f>
-        <v>314.76598220399967</v>
+        <v>275.51902728257994</v>
       </c>
       <c r="E72" s="3">
         <f t="shared" si="4"/>
-        <v>398.25619815959959</v>
+        <v>335.97698965757326</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I72" s="3">
         <f>I71*$B$28</f>
-        <v>207.25486635359994</v>
+        <v>187.99573679999995</v>
       </c>
       <c r="J72" s="3">
         <f t="shared" ref="J72:K72" si="5">J71*$B$28</f>
-        <v>242.87339728703995</v>
+        <v>222.37815815999997</v>
       </c>
       <c r="K72" s="3">
         <f t="shared" si="5"/>
-        <v>297.07105474444791</v>
+        <v>263.13366379199999</v>
       </c>
       <c r="M72" s="13" t="s">
         <v>39</v>
       </c>
       <c r="O72" s="3">
         <f>O71*$B$28</f>
-        <v>314.74330906799997</v>
+        <v>250.76241749999997</v>
       </c>
       <c r="P72" s="3">
         <f t="shared" ref="P72:Q72" si="6">P71*$B$28</f>
-        <v>390.11228296752</v>
+        <v>311.22547687499997</v>
       </c>
       <c r="Q72" s="3">
         <f t="shared" si="6"/>
-        <v>495.06550370940005</v>
+        <v>386.65957359375</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.3">
@@ -2400,15 +2400,15 @@
       <c r="B73" s="16"/>
       <c r="C73" s="6">
         <f>C71-C72</f>
-        <v>771.46347683999943</v>
+        <v>665.9290576343999</v>
       </c>
       <c r="D73" s="6">
         <f>D71-D72</f>
-        <v>935.79413779599906</v>
+        <v>819.11358011741993</v>
       </c>
       <c r="E73" s="6">
         <f>E71-E72</f>
-        <v>1184.0091898403989</v>
+        <v>998.85411744442627</v>
       </c>
       <c r="G73" s="17" t="s">
         <v>40</v>
@@ -2416,15 +2416,15 @@
       <c r="H73" s="16"/>
       <c r="I73" s="6">
         <f>I71-I72</f>
-        <v>616.16534164639984</v>
+        <v>558.90826319999996</v>
       </c>
       <c r="J73" s="6">
         <f>J71-J72</f>
-        <v>722.05865391295993</v>
+        <v>661.12664183999993</v>
       </c>
       <c r="K73" s="6">
         <f>K71-K72</f>
-        <v>883.18740669555189</v>
+        <v>782.29209620800009</v>
       </c>
       <c r="M73" s="17" t="s">
         <v>40</v>
@@ -2432,15 +2432,15 @@
       <c r="N73" s="16"/>
       <c r="O73" s="6">
         <f>O71-O72</f>
-        <v>935.72673093200001</v>
+        <v>745.51258250000001</v>
       </c>
       <c r="P73" s="6">
         <f>P71-P72</f>
-        <v>1159.7974626324801</v>
+        <v>925.26827312500018</v>
       </c>
       <c r="Q73" s="6">
         <f>Q71-Q72</f>
-        <v>1471.8216782906004</v>
+        <v>1149.5326139062499</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.3">
@@ -2449,45 +2449,45 @@
       </c>
       <c r="C74" s="3">
         <f>C70</f>
-        <v>130.30000000000001</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="D74" s="3">
         <f t="shared" ref="D74:E74" si="7">D70</f>
-        <v>143.19999999999999</v>
+        <v>107.1</v>
       </c>
       <c r="E74" s="3">
         <f t="shared" si="7"/>
-        <v>149.5</v>
+        <v>143.30000000000001</v>
       </c>
       <c r="G74" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I74" s="3">
         <f>I70</f>
-        <v>130.30000000000001</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="J74" s="3">
         <f t="shared" ref="J74:K74" si="8">J70</f>
-        <v>143.19999999999999</v>
+        <v>107.1</v>
       </c>
       <c r="K74" s="3">
         <f t="shared" si="8"/>
-        <v>149.5</v>
+        <v>143.30000000000001</v>
       </c>
       <c r="M74" s="13" t="s">
         <v>41</v>
       </c>
       <c r="O74" s="3">
         <f>O70</f>
-        <v>130.30000000000001</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="P74" s="3">
         <f t="shared" ref="P74:Q74" si="9">P70</f>
-        <v>143.19999999999999</v>
+        <v>107.1</v>
       </c>
       <c r="Q74" s="3">
         <f t="shared" si="9"/>
-        <v>149.5</v>
+        <v>143.30000000000001</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.3">
@@ -2496,45 +2496,45 @@
       </c>
       <c r="C75" s="3">
         <f>('DCF &amp; Valuation'!B32)</f>
-        <v>195</v>
+        <v>290</v>
       </c>
       <c r="D75" s="3">
         <f>('DCF &amp; Valuation'!B33)</f>
-        <v>174.4</v>
+        <v>375</v>
       </c>
       <c r="E75" s="3">
         <f>('DCF &amp; Valuation'!B34)</f>
-        <v>216.3</v>
+        <v>192.8</v>
       </c>
       <c r="G75" s="13" t="s">
         <v>42</v>
       </c>
       <c r="I75" s="3">
         <f>B32</f>
-        <v>195</v>
+        <v>290</v>
       </c>
       <c r="J75" s="3">
         <f>B33</f>
-        <v>174.4</v>
+        <v>375</v>
       </c>
       <c r="K75" s="3">
         <f>B34</f>
-        <v>216.3</v>
+        <v>192.8</v>
       </c>
       <c r="M75" s="13" t="s">
         <v>42</v>
       </c>
       <c r="O75" s="3">
         <f>B32</f>
-        <v>195</v>
+        <v>290</v>
       </c>
       <c r="P75" s="3">
         <f>B33</f>
-        <v>174.4</v>
+        <v>375</v>
       </c>
       <c r="Q75" s="3">
         <f>B34</f>
-        <v>216.3</v>
+        <v>192.8</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.3">
@@ -2543,45 +2543,45 @@
       </c>
       <c r="C76" s="3">
         <f>('DCF &amp; Valuation'!B35)</f>
-        <v>346.9</v>
+        <v>186.5</v>
       </c>
       <c r="D76" s="3">
         <f>('DCF &amp; Valuation'!B36)</f>
-        <v>475.5</v>
+        <v>337.2</v>
       </c>
       <c r="E76" s="3">
         <f>('DCF &amp; Valuation'!B37)</f>
-        <v>512.6</v>
+        <v>471.3</v>
       </c>
       <c r="G76" s="13" t="s">
         <v>43</v>
       </c>
       <c r="I76" s="3">
         <f>B35</f>
-        <v>346.9</v>
+        <v>186.5</v>
       </c>
       <c r="J76" s="3">
         <f>B36</f>
-        <v>475.5</v>
+        <v>337.2</v>
       </c>
       <c r="K76" s="3">
         <f>B37</f>
-        <v>512.6</v>
+        <v>471.3</v>
       </c>
       <c r="M76" s="13" t="s">
         <v>43</v>
       </c>
       <c r="O76" s="3">
         <f>B35</f>
-        <v>346.9</v>
+        <v>186.5</v>
       </c>
       <c r="P76" s="3">
         <f>B36</f>
-        <v>475.5</v>
+        <v>337.2</v>
       </c>
       <c r="Q76" s="3">
         <f>B37</f>
-        <v>512.6</v>
+        <v>471.3</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.3">
@@ -2591,15 +2591,15 @@
       <c r="B77" s="16"/>
       <c r="C77" s="6">
         <f>C73+C74-C75-C76</f>
-        <v>359.86347683999941</v>
+        <v>268.02905763439992</v>
       </c>
       <c r="D77" s="6">
         <f>D73+D74-D75-D76</f>
-        <v>429.09413779599902</v>
+        <v>214.01358011741996</v>
       </c>
       <c r="E77" s="6">
         <f>E73+E74-E75-E76</f>
-        <v>604.60918984039893</v>
+        <v>478.05411744442625</v>
       </c>
       <c r="G77" s="17" t="s">
         <v>44</v>
@@ -2607,15 +2607,15 @@
       <c r="H77" s="16"/>
       <c r="I77" s="6">
         <f>I73+I74-I75-I76</f>
-        <v>204.56534164639982</v>
+        <v>161.00826319999999</v>
       </c>
       <c r="J77" s="6">
         <f>J73+J74-J75-J76</f>
-        <v>215.35865391295999</v>
+        <v>56.026641839999968</v>
       </c>
       <c r="K77" s="6">
         <f>K73+K74-K75-K76</f>
-        <v>303.78740669555202</v>
+        <v>261.49209620800019</v>
       </c>
       <c r="M77" s="17" t="s">
         <v>44</v>
@@ -2623,15 +2623,15 @@
       <c r="N77" s="16"/>
       <c r="O77" s="6">
         <f>O73+O74-O75-O76</f>
-        <v>524.12673093199999</v>
+        <v>347.61258250000003</v>
       </c>
       <c r="P77" s="6">
         <f>P73+P74-P75-P76</f>
-        <v>653.09746263248007</v>
+        <v>320.1682731250001</v>
       </c>
       <c r="Q77" s="6">
         <f>Q73+Q74-Q75-Q76</f>
-        <v>892.42167829060043</v>
+        <v>628.73261390624998</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.3">
@@ -2641,15 +2641,15 @@
       <c r="B78" s="16"/>
       <c r="C78" s="6">
         <f>C77/(1+$B$46)^1</f>
-        <v>311.36885662498088</v>
+        <v>231.90989524896946</v>
       </c>
       <c r="D78" s="6">
         <f>D77/(1+$B$46)^2</f>
-        <v>321.23834659160747</v>
+        <v>160.21978062481827</v>
       </c>
       <c r="E78" s="6">
         <f>E77/(1+$B$46)^3</f>
-        <v>391.63991255519375</v>
+        <v>309.66296228809881</v>
       </c>
       <c r="G78" s="17" t="s">
         <v>139</v>
@@ -2657,15 +2657,15 @@
       <c r="H78" s="16"/>
       <c r="I78" s="6">
         <f>I77/(1+$B$46)^1</f>
-        <v>176.99844700232794</v>
+        <v>139.31105001257973</v>
       </c>
       <c r="J78" s="6">
         <f>J77/(1+$B$46)^2</f>
-        <v>161.22676078153253</v>
+        <v>41.943956359334777</v>
       </c>
       <c r="K78" s="6">
         <f>K77/(1+$B$46)^3</f>
-        <v>196.78045817500964</v>
+        <v>169.3833693130091</v>
       </c>
       <c r="M78" s="17" t="s">
         <v>139</v>
@@ -2673,15 +2673,15 @@
       <c r="N78" s="16"/>
       <c r="O78" s="6">
         <f>O77/(1+$B$46)^1</f>
-        <v>453.49626022049887</v>
+        <v>300.76887299570291</v>
       </c>
       <c r="P78" s="6">
         <f>P77/(1+$B$46)^2</f>
-        <v>488.93688023063987</v>
+        <v>239.69175439693976</v>
       </c>
       <c r="Q78" s="6">
         <f>Q77/(1+$B$46)^3</f>
-        <v>578.07250356275767</v>
+        <v>407.26603245286805</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.3">
@@ -2712,15 +2712,15 @@
       </c>
       <c r="B82" s="3">
         <f>E64</f>
-        <v>1329.7584614399998</v>
+        <v>1188.72576</v>
       </c>
       <c r="C82" s="3">
         <f>E65</f>
-        <v>1731.7653879999984</v>
+        <v>1478.1311071019995</v>
       </c>
       <c r="D82" s="3">
         <f>E66</f>
-        <v>2116.3871820000004</v>
+        <v>1679.4921875</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -2729,15 +2729,15 @@
       </c>
       <c r="B83" s="3">
         <f>B82*$B$48</f>
-        <v>13297.584614399999</v>
+        <v>11887.257600000001</v>
       </c>
       <c r="C83" s="3">
         <f>C82*$B$48</f>
-        <v>17317.653879999983</v>
+        <v>14781.311071019994</v>
       </c>
       <c r="D83" s="3">
         <f>D82*$B$48</f>
-        <v>21163.871820000004</v>
+        <v>16794.921875</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -2746,15 +2746,15 @@
       </c>
       <c r="B84" s="7">
         <f>B83/(1+$B$46)^3</f>
-        <v>8613.6052231585272</v>
+        <v>7700.0558463459674</v>
       </c>
       <c r="C84" s="7">
         <f t="shared" ref="C84:D84" si="10">C83/(1+$B$46)^3</f>
-        <v>11217.63374621324</v>
+        <v>9574.6996118823809</v>
       </c>
       <c r="D84" s="7">
         <f t="shared" si="10"/>
-        <v>13709.048833846058</v>
+        <v>10879.030363783613</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -2763,15 +2763,15 @@
       </c>
       <c r="B85" s="3">
         <f>SUM(I78:K78)</f>
-        <v>535.00566595887017</v>
+        <v>350.63837568492363</v>
       </c>
       <c r="C85" s="3">
         <f>SUM($C$78:$E$78)</f>
-        <v>1024.2471157717821</v>
+        <v>701.79263816188654</v>
       </c>
       <c r="D85" s="3">
         <f>SUM(O78:Q78)</f>
-        <v>1520.5056440138965</v>
+        <v>947.72665984551077</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -2780,15 +2780,15 @@
       </c>
       <c r="B86" s="5">
         <f>B84+B85</f>
-        <v>9148.6108891173972</v>
+        <v>8050.6942220308911</v>
       </c>
       <c r="C86" s="5">
         <f>C84+C85</f>
-        <v>12241.880861985022</v>
+        <v>10276.492250044268</v>
       </c>
       <c r="D86" s="5">
         <f>D84+D85</f>
-        <v>15229.554477859954</v>
+        <v>11826.757023629125</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -2797,15 +2797,15 @@
       </c>
       <c r="B87" s="3">
         <f>'DCF &amp; Valuation'!$B$12</f>
-        <v>151.19999999999993</v>
+        <v>-183</v>
       </c>
       <c r="C87" s="3">
         <f>'DCF &amp; Valuation'!$B$12</f>
-        <v>151.19999999999993</v>
+        <v>-183</v>
       </c>
       <c r="D87" s="3">
         <f>'DCF &amp; Valuation'!$B$12</f>
-        <v>151.19999999999993</v>
+        <v>-183</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -2814,15 +2814,15 @@
       </c>
       <c r="B88" s="5">
         <f>B86-B87</f>
-        <v>8997.4108891173964</v>
+        <v>8233.694222030892</v>
       </c>
       <c r="C88" s="5">
         <f>C86-C87</f>
-        <v>12090.680861985022</v>
+        <v>10459.492250044268</v>
       </c>
       <c r="D88" s="5">
         <f>D86-D87</f>
-        <v>15078.354477859953</v>
+        <v>12009.757023629125</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -2831,15 +2831,15 @@
       </c>
       <c r="B89" s="6">
         <f>B88/'DCF &amp; Valuation'!$B$7</f>
-        <v>670.198204031091</v>
+        <v>613.31055657585785</v>
       </c>
       <c r="C89" s="6">
         <f>C88/'DCF &amp; Valuation'!$B$7</f>
-        <v>900.60937519441495</v>
+        <v>779.10556797350227</v>
       </c>
       <c r="D89" s="6">
         <f>D88/'DCF &amp; Valuation'!$B$7</f>
-        <v>1123.1548959299778</v>
+        <v>894.58152876194595</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -2848,15 +2848,15 @@
       </c>
       <c r="B90" s="3">
         <f>'DCF &amp; Valuation'!$B$8</f>
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="C90" s="3">
         <f>'DCF &amp; Valuation'!$B$8</f>
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="D90" s="3">
         <f>'DCF &amp; Valuation'!$B$8</f>
-        <v>513</v>
+        <v>489</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -2865,15 +2865,15 @@
       </c>
       <c r="B91" s="62">
         <f>B89/B90-1</f>
-        <v>0.30642924762395896</v>
+        <v>0.25421381712854374</v>
       </c>
       <c r="C91" s="62">
         <f>C89/C90-1</f>
-        <v>0.75557383078833329</v>
+        <v>0.59326292019121118</v>
       </c>
       <c r="D91" s="62">
         <f>D89/D90-1</f>
-        <v>1.1893857620467405</v>
+        <v>0.82941007926778321</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -2913,23 +2913,23 @@
       </c>
       <c r="B95" s="3">
         <f>((E77*(1+0.02)/(0.12-0.02)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>397.17581674580924</v>
+        <v>328.0402331495012</v>
       </c>
       <c r="C95" s="3">
         <f>((E77*(1+0.03)/(0.12-0.03)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>437.06745708943419</v>
+        <v>359.58186903319699</v>
       </c>
       <c r="D95" s="3">
         <f>((E77*(1+0.04)/(0.12-0.04)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>486.93200751896541</v>
+        <v>399.00891388781662</v>
       </c>
       <c r="E95" s="3">
         <f>((E77*(1+0.05)/(0.12-0.05)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>551.04357235693396</v>
+        <v>449.70082870089891</v>
       </c>
       <c r="F95" s="3">
         <f>((E77*(1+0.06)/(0.12-0.06)/(1+0.12)^3)+(C77/(1+0.12)^1+D77/(1+0.12)^2+E77/(1+0.12)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>636.5256588075589</v>
+        <v>517.29004845167537</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
@@ -2938,23 +2938,23 @@
       </c>
       <c r="B96" s="3">
         <f>((E77*(1+0.02)/(0.13-0.02)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>358.12523533368028</v>
+        <v>297.30439380094043</v>
       </c>
       <c r="C96" s="3">
         <f>((E77*(1+0.03)/(0.13-0.03)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>390.18873164387679</v>
+        <v>322.65645044897093</v>
       </c>
       <c r="D96" s="3">
         <f>((E77*(1+0.04)/(0.13-0.04)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>429.37744935633924</v>
+        <v>353.64229746323042</v>
       </c>
       <c r="E96" s="3">
         <f>((E77*(1+0.05)/(0.13-0.05)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>478.36334649691713</v>
+        <v>392.37460623105466</v>
       </c>
       <c r="F96" s="3">
         <f>((E77*(1+0.06)/(0.13-0.06)/(1+0.13)^3)+(C77/(1+0.13)^1+D77/(1+0.13)^2+E77/(1+0.13)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>541.3452142490886</v>
+        <v>442.17328893254302</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -2963,23 +2963,23 @@
       </c>
       <c r="B97" s="3">
         <f>((E77*(1+0.02)/(0.14-0.02)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>325.62655845002894</v>
+        <v>271.74542849497425</v>
       </c>
       <c r="C97" s="3">
         <f>((E77*(1+0.03)/(0.14-0.03)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>351.87943012752572</v>
+        <v>292.50312389732244</v>
       </c>
       <c r="D97" s="3">
         <f>((E77*(1+0.04)/(0.14-0.04)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>383.38287614052206</v>
+        <v>317.41235838014029</v>
       </c>
       <c r="E97" s="3">
         <f>((E77*(1+0.05)/(0.14-0.05)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>421.88708793418397</v>
+        <v>347.85697830358424</v>
       </c>
       <c r="F97" s="3">
         <f>((E77*(1+0.06)/(0.14-0.06)/(1+0.14)^3)+(C77/(1+0.14)^1+D77/(1+0.14)^2+E77/(1+0.14)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>470.01735267626145</v>
+        <v>385.91275320788924</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -2988,23 +2988,23 @@
       </c>
       <c r="B98" s="3">
         <f>((E77*(1+0.02)/(0.15-0.02)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>298.16646048086079</v>
+        <v>250.16689999283881</v>
       </c>
       <c r="C98" s="3">
         <f>((E77*(1+0.03)/(0.15-0.03)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>319.99577863428954</v>
+        <v>267.42696748702576</v>
       </c>
       <c r="D98" s="10">
         <f>((E77*(1+0.04)/(0.15-0.04)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>345.79406372470538</v>
+        <v>287.82522907106488</v>
       </c>
       <c r="E98" s="3">
         <f>((E77*(1+0.05)/(0.15-0.05)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>376.75200583320424</v>
+        <v>312.30314297191183</v>
       </c>
       <c r="F98" s="3">
         <f>((E77*(1+0.06)/(0.15-0.06)/(1+0.15)^3)+(C77/(1+0.15)^1+D77/(1+0.15)^2+E77/(1+0.15)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>414.5894906324807</v>
+        <v>342.22059329516912</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
@@ -3013,23 +3013,23 @@
       </c>
       <c r="B99" s="3">
         <f>((E77*(1+0.02)/(0.16-0.02)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>274.6640472579067</v>
+        <v>231.71428192658331</v>
       </c>
       <c r="C99" s="3">
         <f>((E77*(1+0.03)/(0.16-0.03)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>293.05368114905002</v>
+        <v>246.25465006468141</v>
       </c>
       <c r="D99" s="3">
         <f>((E77*(1+0.04)/(0.16-0.04)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>314.50825402205055</v>
+        <v>263.21841289246254</v>
       </c>
       <c r="E99" s="3">
         <f>((E77*(1+0.05)/(0.16-0.05)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>339.86365832650569</v>
+        <v>283.26649623438561</v>
       </c>
       <c r="F99" s="3">
         <f>((E77*(1+0.06)/(0.16-0.06)/(1+0.16)^3)+(C77/(1+0.16)^1+D77/(1+0.16)^2+E77/(1+0.16)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>370.29014349185195</v>
+        <v>307.32419624469333</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -3038,23 +3038,23 @@
       </c>
       <c r="B100" s="3">
         <f>((E77*(1+0.02)/(0.17-0.02)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>254.32670976387129</v>
+        <v>215.76098506306161</v>
       </c>
       <c r="C100" s="3">
         <f>((E77*(1+0.03)/(0.17-0.03)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>269.99311771823818</v>
+        <v>228.14814515589151</v>
       </c>
       <c r="D100" s="3">
         <f>((E77*(1+0.04)/(0.17-0.04)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>288.06974228096919</v>
+        <v>242.44102218607978</v>
       </c>
       <c r="E100" s="3">
         <f>((E77*(1+0.05)/(0.17-0.05)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>309.15913760415532</v>
+        <v>259.11604538796615</v>
       </c>
       <c r="F100" s="3">
         <f>((E77*(1+0.06)/(0.17-0.06)/(1+0.17)^3)+(C77/(1+0.17)^1+D77/(1+0.17)^2+E77/(1+0.17)^3)-'DCF &amp; Valuation'!B12)/'DCF &amp; Valuation'!B7</f>
-        <v>334.08296844064802</v>
+        <v>278.8228909901955</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
